--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_ADJR2.xlsx
@@ -211,7 +211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,13 +227,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -243,12 +236,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -260,49 +268,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -605,8 +576,8 @@
   <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -664,49 +635,49 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.23286925644907919</v>
+        <v>0.23443226001683981</v>
       </c>
       <c r="C2">
-        <v>0.36017020723419918</v>
+        <v>0.3630596967281467</v>
       </c>
       <c r="D2">
-        <v>0.38978733007388311</v>
+        <v>0.39420933268981989</v>
       </c>
       <c r="E2">
-        <v>0.4296908440060232</v>
+        <v>0.43434064896296232</v>
       </c>
       <c r="F2">
-        <v>0.4481217503069086</v>
+        <v>0.45161303785808488</v>
       </c>
       <c r="G2">
-        <v>0.48926949278024717</v>
+        <v>0.49558818561362061</v>
       </c>
       <c r="H2">
-        <v>0.49297216897053381</v>
+        <v>0.4982150515590385</v>
       </c>
       <c r="I2">
-        <v>0.47651872698419617</v>
+        <v>0.4827046326125467</v>
       </c>
       <c r="J2">
-        <v>0.47029927535508242</v>
+        <v>0.47016236860429922</v>
       </c>
       <c r="K2">
-        <v>0.45763240868075328</v>
+        <v>0.45723842629909173</v>
       </c>
       <c r="L2">
-        <v>0.48651258735925063</v>
+        <v>0.48388859315829452</v>
       </c>
       <c r="M2">
-        <v>0.45833062028651322</v>
+        <v>0.45416917061075451</v>
       </c>
       <c r="N2">
-        <v>0.46954316458260209</v>
+        <v>0.4659709914505018</v>
       </c>
       <c r="O2">
-        <v>0.45822615279323159</v>
+        <v>0.45453378580358372</v>
       </c>
       <c r="P2">
-        <v>0.4744297938922703</v>
+        <v>0.47241063118006349</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -714,49 +685,49 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>0.2920373267063972</v>
+        <v>0.29353238472880122</v>
       </c>
       <c r="C3">
-        <v>0.384087003690471</v>
+        <v>0.38687193316261109</v>
       </c>
       <c r="D3">
-        <v>0.39557461329699378</v>
+        <v>0.39733231735765218</v>
       </c>
       <c r="E3">
-        <v>0.39659943094820321</v>
+        <v>0.38376029136400031</v>
       </c>
       <c r="F3">
-        <v>0.3533002909907923</v>
+        <v>0.34740406742365548</v>
       </c>
       <c r="G3">
-        <v>0.38242196668825512</v>
+        <v>0.3756694833442048</v>
       </c>
       <c r="H3">
-        <v>0.35300534799212352</v>
+        <v>0.34999677543213481</v>
       </c>
       <c r="I3">
-        <v>0.33590865306832651</v>
+        <v>0.33330769352427808</v>
       </c>
       <c r="J3">
-        <v>0.32854359923282639</v>
+        <v>0.33253638286536752</v>
       </c>
       <c r="K3">
-        <v>0.32623812471113561</v>
+        <v>0.32876805217774591</v>
       </c>
       <c r="L3">
-        <v>0.30018405155595951</v>
+        <v>0.30002246948384959</v>
       </c>
       <c r="M3">
-        <v>0.27254507187552629</v>
+        <v>0.27399091103805778</v>
       </c>
       <c r="N3">
-        <v>0.2355017976161678</v>
+        <v>0.23647884334613459</v>
       </c>
       <c r="O3">
-        <v>0.18818115913704289</v>
+        <v>0.1968230250412554</v>
       </c>
       <c r="P3">
-        <v>0.17060611971853379</v>
+        <v>0.1809183539949944</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -764,49 +735,49 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>0.25282641776832671</v>
+        <v>0.25026553797456358</v>
       </c>
       <c r="C4">
-        <v>0.34750564945149393</v>
+        <v>0.34224761827082029</v>
       </c>
       <c r="D4">
-        <v>0.35831129644829679</v>
+        <v>0.35454744075856159</v>
       </c>
       <c r="E4">
-        <v>0.34400642434073642</v>
+        <v>0.33571439610876541</v>
       </c>
       <c r="F4">
-        <v>0.36190869332918452</v>
+        <v>0.35449316123792868</v>
       </c>
       <c r="G4">
-        <v>0.35773113593668843</v>
+        <v>0.34427714197406561</v>
       </c>
       <c r="H4">
-        <v>0.38674330500895859</v>
+        <v>0.37589255177246877</v>
       </c>
       <c r="I4">
-        <v>0.38575815482729892</v>
+        <v>0.37556714728691049</v>
       </c>
       <c r="J4">
-        <v>0.392739056750533</v>
+        <v>0.38217935313673812</v>
       </c>
       <c r="K4">
-        <v>0.34338402836898219</v>
+        <v>0.3325670083540283</v>
       </c>
       <c r="L4">
-        <v>0.34194629835329121</v>
+        <v>0.33219659004307078</v>
       </c>
       <c r="M4">
-        <v>0.35230848501666012</v>
+        <v>0.34112662495125751</v>
       </c>
       <c r="N4">
-        <v>0.36639387775458188</v>
+        <v>0.36038946849715031</v>
       </c>
       <c r="O4">
-        <v>0.34949002185059658</v>
+        <v>0.34844290613413609</v>
       </c>
       <c r="P4">
-        <v>0.31800666213414819</v>
+        <v>0.31458411516062501</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -814,49 +785,49 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>0.37399106541480498</v>
+        <v>0.37214729399021651</v>
       </c>
       <c r="C5">
-        <v>0.37407094840634952</v>
+        <v>0.37525172072318058</v>
       </c>
       <c r="D5">
-        <v>0.37403059851907672</v>
+        <v>0.37658097199594059</v>
       </c>
       <c r="E5">
-        <v>0.33906284988385349</v>
+        <v>0.34356113839716268</v>
       </c>
       <c r="F5">
-        <v>0.3392632291942807</v>
+        <v>0.33925646888910188</v>
       </c>
       <c r="G5">
-        <v>0.32077406356229943</v>
+        <v>0.31287654579736562</v>
       </c>
       <c r="H5">
-        <v>0.32310485293530289</v>
+        <v>0.31474712716744491</v>
       </c>
       <c r="I5">
-        <v>0.36554109023998088</v>
+        <v>0.35619789623149872</v>
       </c>
       <c r="J5">
-        <v>0.38317194177024722</v>
+        <v>0.37563615703787762</v>
       </c>
       <c r="K5">
-        <v>0.36648854085182608</v>
+        <v>0.35744952560358267</v>
       </c>
       <c r="L5">
-        <v>0.36550752690746868</v>
+        <v>0.35222868904047783</v>
       </c>
       <c r="M5">
-        <v>0.35027165455561848</v>
+        <v>0.33466966214806942</v>
       </c>
       <c r="N5">
-        <v>0.32047313797800869</v>
+        <v>0.29900193205342612</v>
       </c>
       <c r="O5">
-        <v>0.32526891258943208</v>
+        <v>0.3066650490399358</v>
       </c>
       <c r="P5">
-        <v>0.31057341684669137</v>
+        <v>0.28568744555473891</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -864,49 +835,49 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.37659405199061008</v>
+        <v>0.37589567217220171</v>
       </c>
       <c r="C6">
-        <v>0.38441183974336091</v>
+        <v>0.38623354450824471</v>
       </c>
       <c r="D6">
-        <v>0.38813639694809349</v>
+        <v>0.38823266164569331</v>
       </c>
       <c r="E6">
-        <v>0.29968771278093531</v>
+        <v>0.29971113931803772</v>
       </c>
       <c r="F6">
-        <v>0.35527952665790741</v>
+        <v>0.35073134942858469</v>
       </c>
       <c r="G6">
-        <v>0.3244687851227247</v>
+        <v>0.31319051116298557</v>
       </c>
       <c r="H6">
-        <v>0.35413381233363161</v>
+        <v>0.34839862028937701</v>
       </c>
       <c r="I6">
-        <v>0.39823904177831559</v>
+        <v>0.39358376490181751</v>
       </c>
       <c r="J6">
-        <v>0.38468032562687532</v>
+        <v>0.37803304711620761</v>
       </c>
       <c r="K6">
-        <v>0.36858038413400251</v>
+        <v>0.36358352227346852</v>
       </c>
       <c r="L6">
-        <v>0.33741365948325069</v>
+        <v>0.33891028268713369</v>
       </c>
       <c r="M6">
-        <v>0.30760773866092761</v>
+        <v>0.31081918079435877</v>
       </c>
       <c r="N6">
-        <v>0.30184923289674359</v>
+        <v>0.29945211133329602</v>
       </c>
       <c r="O6">
-        <v>0.30342646316068173</v>
+        <v>0.30020695080035548</v>
       </c>
       <c r="P6">
-        <v>0.33589594244582338</v>
+        <v>0.33233895914048922</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -914,49 +885,49 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>0.2485721114974139</v>
+        <v>0.25111563245403512</v>
       </c>
       <c r="C7">
-        <v>0.35718901442131751</v>
+        <v>0.3610921640649904</v>
       </c>
       <c r="D7">
-        <v>0.4116513750700046</v>
+        <v>0.4170052628765426</v>
       </c>
       <c r="E7">
-        <v>0.44758331564249348</v>
+        <v>0.4511703684369725</v>
       </c>
       <c r="F7">
-        <v>0.46315025262209092</v>
+        <v>0.46360969053802631</v>
       </c>
       <c r="G7">
-        <v>0.49260928986954472</v>
+        <v>0.49142564058712512</v>
       </c>
       <c r="H7">
-        <v>0.47090974960579618</v>
+        <v>0.46319029049319282</v>
       </c>
       <c r="I7">
-        <v>0.49454062585687619</v>
+        <v>0.48807918836053532</v>
       </c>
       <c r="J7">
-        <v>0.49713743855988662</v>
+        <v>0.49445870885636273</v>
       </c>
       <c r="K7">
-        <v>0.50313272521558972</v>
+        <v>0.49223932815465887</v>
       </c>
       <c r="L7">
-        <v>0.48978653361397151</v>
+        <v>0.4815710226806218</v>
       </c>
       <c r="M7">
-        <v>0.4685230446573671</v>
+        <v>0.46139128969495952</v>
       </c>
       <c r="N7">
-        <v>0.48481046465416078</v>
+        <v>0.48163820938522012</v>
       </c>
       <c r="O7">
-        <v>0.50445665383654614</v>
+        <v>0.50110382104943985</v>
       </c>
       <c r="P7">
-        <v>0.49691849661155041</v>
+        <v>0.49014058632648899</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -964,49 +935,49 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>0.29333159826107158</v>
+        <v>0.29552871778744128</v>
       </c>
       <c r="C8">
-        <v>0.33819714390915279</v>
+        <v>0.34105232914662159</v>
       </c>
       <c r="D8">
-        <v>0.34245994647812528</v>
+        <v>0.34223353507824622</v>
       </c>
       <c r="E8">
-        <v>0.36070330189727429</v>
+        <v>0.35889828836962251</v>
       </c>
       <c r="F8">
-        <v>0.41050904507374469</v>
+        <v>0.41198993559429531</v>
       </c>
       <c r="G8">
-        <v>0.38178907875520851</v>
+        <v>0.38217773759352958</v>
       </c>
       <c r="H8">
-        <v>0.41481757379940498</v>
+        <v>0.41855619153483931</v>
       </c>
       <c r="I8">
-        <v>0.42981831114119912</v>
+        <v>0.43095183727945091</v>
       </c>
       <c r="J8">
-        <v>0.41447197906408723</v>
+        <v>0.40946782351457173</v>
       </c>
       <c r="K8">
-        <v>0.40439112791217008</v>
+        <v>0.40029182870197849</v>
       </c>
       <c r="L8">
-        <v>0.39072707348497249</v>
+        <v>0.39220198492496111</v>
       </c>
       <c r="M8">
-        <v>0.39906059152946199</v>
+        <v>0.40234022584104501</v>
       </c>
       <c r="N8">
-        <v>0.40899316920269191</v>
+        <v>0.4091309349918934</v>
       </c>
       <c r="O8">
-        <v>0.40848479307389962</v>
+        <v>0.40728752803009488</v>
       </c>
       <c r="P8">
-        <v>0.38811691851787489</v>
+        <v>0.38428415321944409</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1014,49 +985,49 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>0.29473163608288711</v>
+        <v>0.2933052292351776</v>
       </c>
       <c r="C9">
-        <v>0.34026579823802511</v>
+        <v>0.33717824959894233</v>
       </c>
       <c r="D9">
-        <v>0.34139840101148661</v>
+        <v>0.33860091841515011</v>
       </c>
       <c r="E9">
-        <v>0.3585212522673889</v>
+        <v>0.35594565444380011</v>
       </c>
       <c r="F9">
-        <v>0.40805969954194682</v>
+        <v>0.40311144541242122</v>
       </c>
       <c r="G9">
-        <v>0.38292991870394189</v>
+        <v>0.3754011974981627</v>
       </c>
       <c r="H9">
-        <v>0.41860047105373838</v>
+        <v>0.4110534872957517</v>
       </c>
       <c r="I9">
-        <v>0.43537393939100372</v>
+        <v>0.42769479844041192</v>
       </c>
       <c r="J9">
-        <v>0.41451867666052711</v>
+        <v>0.41136392308359682</v>
       </c>
       <c r="K9">
-        <v>0.39667329365650789</v>
+        <v>0.39335715602424137</v>
       </c>
       <c r="L9">
-        <v>0.38282431072074141</v>
+        <v>0.3832009465473345</v>
       </c>
       <c r="M9">
-        <v>0.38632663061389272</v>
+        <v>0.3847653390167482</v>
       </c>
       <c r="N9">
-        <v>0.40385080006977608</v>
+        <v>0.40211532514905979</v>
       </c>
       <c r="O9">
-        <v>0.4298723404345548</v>
+        <v>0.4311531914444896</v>
       </c>
       <c r="P9">
-        <v>0.39644777181236313</v>
+        <v>0.39786758766610097</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1064,49 +1035,49 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>0.29360963256590311</v>
+        <v>0.29404309696364789</v>
       </c>
       <c r="C10">
-        <v>0.33968879642518779</v>
+        <v>0.33787331677511601</v>
       </c>
       <c r="D10">
-        <v>0.34090139303934119</v>
+        <v>0.34079349782344992</v>
       </c>
       <c r="E10">
-        <v>0.35695881670576241</v>
+        <v>0.35853764868921573</v>
       </c>
       <c r="F10">
-        <v>0.40348287619054068</v>
+        <v>0.40826924107930512</v>
       </c>
       <c r="G10">
-        <v>0.37453937548300448</v>
+        <v>0.37895758822489328</v>
       </c>
       <c r="H10">
-        <v>0.41209393517301529</v>
+        <v>0.41647859267879389</v>
       </c>
       <c r="I10">
-        <v>0.42894210738969202</v>
+        <v>0.43256694881923768</v>
       </c>
       <c r="J10">
-        <v>0.41246216428392002</v>
+        <v>0.41553017266310072</v>
       </c>
       <c r="K10">
-        <v>0.38993405162905942</v>
+        <v>0.39549620438988747</v>
       </c>
       <c r="L10">
-        <v>0.3780818356351629</v>
+        <v>0.38854236964838351</v>
       </c>
       <c r="M10">
-        <v>0.38352417838661162</v>
+        <v>0.39312861417965989</v>
       </c>
       <c r="N10">
-        <v>0.41186615318910802</v>
+        <v>0.41350679622723119</v>
       </c>
       <c r="O10">
-        <v>0.44562758479563153</v>
+        <v>0.44460623948698558</v>
       </c>
       <c r="P10">
-        <v>0.4152394107616868</v>
+        <v>0.41706492693156738</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1114,49 +1085,49 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>0.29328838768455129</v>
+        <v>0.29230423562794311</v>
       </c>
       <c r="C11">
-        <v>0.33657614773258021</v>
+        <v>0.33926836877636563</v>
       </c>
       <c r="D11">
-        <v>0.3394273534487694</v>
+        <v>0.3465700021462349</v>
       </c>
       <c r="E11">
-        <v>0.3566346625684812</v>
+        <v>0.36461883404118561</v>
       </c>
       <c r="F11">
-        <v>0.40280929934747639</v>
+        <v>0.40350085038877509</v>
       </c>
       <c r="G11">
-        <v>0.37605380204078931</v>
+        <v>0.38123458880904781</v>
       </c>
       <c r="H11">
-        <v>0.40901277399280123</v>
+        <v>0.41417241379099762</v>
       </c>
       <c r="I11">
-        <v>0.42722007400709677</v>
+        <v>0.42569958860489387</v>
       </c>
       <c r="J11">
-        <v>0.41106448337902679</v>
+        <v>0.41142887599083799</v>
       </c>
       <c r="K11">
-        <v>0.39625654055287468</v>
+        <v>0.38960446611955513</v>
       </c>
       <c r="L11">
-        <v>0.39201411761661598</v>
+        <v>0.37844836406472621</v>
       </c>
       <c r="M11">
-        <v>0.40094226558219731</v>
+        <v>0.38343022566975188</v>
       </c>
       <c r="N11">
-        <v>0.41588896808525899</v>
+        <v>0.39363352049761929</v>
       </c>
       <c r="O11">
-        <v>0.43019627295986163</v>
+        <v>0.4076630607712774</v>
       </c>
       <c r="P11">
-        <v>0.42893237475482282</v>
+        <v>0.41493939929882567</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1164,49 +1135,49 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>0.38302462328042308</v>
+        <v>0.37876921015099202</v>
       </c>
       <c r="C12">
-        <v>0.38560269682873172</v>
+        <v>0.38087791976883167</v>
       </c>
       <c r="D12">
-        <v>0.38179987189485348</v>
+        <v>0.37789686424369517</v>
       </c>
       <c r="E12">
-        <v>0.3379434251250143</v>
+        <v>0.33391885208251759</v>
       </c>
       <c r="F12">
-        <v>0.35580037305280782</v>
+        <v>0.34644237101610209</v>
       </c>
       <c r="G12">
-        <v>0.37164950319431128</v>
+        <v>0.35635111489939802</v>
       </c>
       <c r="H12">
-        <v>0.38721941578814623</v>
+        <v>0.37554053283885169</v>
       </c>
       <c r="I12">
-        <v>0.43594587191603212</v>
+        <v>0.42623720146346761</v>
       </c>
       <c r="J12">
-        <v>0.43961688324795412</v>
+        <v>0.43287570698733208</v>
       </c>
       <c r="K12">
-        <v>0.44342077192933471</v>
+        <v>0.43804929765824002</v>
       </c>
       <c r="L12">
-        <v>0.40923244342925102</v>
+        <v>0.40553474694798303</v>
       </c>
       <c r="M12">
-        <v>0.41277451391907688</v>
+        <v>0.40285050616507601</v>
       </c>
       <c r="N12">
-        <v>0.38008237800761052</v>
+        <v>0.37134209118578781</v>
       </c>
       <c r="O12">
-        <v>0.37501416619561723</v>
+        <v>0.36621042512712709</v>
       </c>
       <c r="P12">
-        <v>0.36748975450251697</v>
+        <v>0.35960712493689811</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1214,49 +1185,49 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>0.38018330635778708</v>
+        <v>0.38270523475625801</v>
       </c>
       <c r="C13">
-        <v>0.40313151051469043</v>
+        <v>0.40230962158880229</v>
       </c>
       <c r="D13">
-        <v>0.41180601618696933</v>
+        <v>0.4098632720542853</v>
       </c>
       <c r="E13">
-        <v>0.40065389348273073</v>
+        <v>0.40072457817242141</v>
       </c>
       <c r="F13">
-        <v>0.35215702352491252</v>
+        <v>0.35164896289084929</v>
       </c>
       <c r="G13">
-        <v>0.3406808053424491</v>
+        <v>0.33659607187056811</v>
       </c>
       <c r="H13">
-        <v>0.35164752116103881</v>
+        <v>0.3460472026165034</v>
       </c>
       <c r="I13">
-        <v>0.37719545248972253</v>
+        <v>0.37280355663993542</v>
       </c>
       <c r="J13">
-        <v>0.38416657633207912</v>
+        <v>0.37418237142171401</v>
       </c>
       <c r="K13">
-        <v>0.38728355350662191</v>
+        <v>0.37577325862268768</v>
       </c>
       <c r="L13">
-        <v>0.39242741057512731</v>
+        <v>0.38110062225578373</v>
       </c>
       <c r="M13">
-        <v>0.38265004891061932</v>
+        <v>0.3697876450735888</v>
       </c>
       <c r="N13">
-        <v>0.36939579017674101</v>
+        <v>0.35663742120465708</v>
       </c>
       <c r="O13">
-        <v>0.35679357760558789</v>
+        <v>0.34449497645607019</v>
       </c>
       <c r="P13">
-        <v>0.33323238773960312</v>
+        <v>0.32512676685810438</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1264,49 +1235,49 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>0.24969422421623849</v>
-      </c>
-      <c r="C14">
-        <v>0.35904117711709721</v>
+        <v>0.2497233182385899</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.35968307540112171</v>
       </c>
       <c r="D14">
-        <v>0.4141361203472067</v>
+        <v>0.41555389083238492</v>
       </c>
       <c r="E14">
-        <v>0.44851132801536342</v>
+        <v>0.44776978434917908</v>
       </c>
       <c r="F14">
-        <v>0.4621001386195146</v>
+        <v>0.46098097018210871</v>
       </c>
       <c r="G14">
-        <v>0.4855570423552773</v>
+        <v>0.48836766249642521</v>
       </c>
       <c r="H14">
-        <v>0.46594028529733228</v>
+        <v>0.46882311218628903</v>
       </c>
       <c r="I14">
-        <v>0.4862087299608977</v>
+        <v>0.48648689757380581</v>
       </c>
       <c r="J14">
-        <v>0.48795775541271108</v>
+        <v>0.48752914163399541</v>
       </c>
       <c r="K14">
-        <v>0.48536619870918352</v>
+        <v>0.48976430344845129</v>
       </c>
       <c r="L14">
-        <v>0.46203009590651423</v>
+        <v>0.46698880715238522</v>
       </c>
       <c r="M14">
-        <v>0.43061459586644912</v>
+        <v>0.43437087234532817</v>
       </c>
       <c r="N14">
-        <v>0.4532920646771107</v>
+        <v>0.45592572090150729</v>
       </c>
       <c r="O14">
-        <v>0.48426792287971038</v>
+        <v>0.48918778128960011</v>
       </c>
       <c r="P14">
-        <v>0.50872984221095185</v>
+        <v>0.5169593738848931</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1314,49 +1285,49 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>0.24850597545414921</v>
-      </c>
-      <c r="C15">
-        <v>0.35663954311013468</v>
+        <v>0.24458666238129431</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.35504457012995999</v>
       </c>
       <c r="D15">
-        <v>0.41198676728673289</v>
+        <v>0.40732729781329191</v>
       </c>
       <c r="E15">
-        <v>0.44599519030810281</v>
+        <v>0.44262163127304421</v>
       </c>
       <c r="F15">
-        <v>0.45682868218345518</v>
+        <v>0.45385969252357661</v>
       </c>
       <c r="G15">
-        <v>0.4823385927322773</v>
+        <v>0.47958677753349632</v>
       </c>
       <c r="H15">
-        <v>0.45841235152172077</v>
+        <v>0.4529901257774514</v>
       </c>
       <c r="I15">
-        <v>0.47717432396197201</v>
+        <v>0.47650788028605462</v>
       </c>
       <c r="J15">
-        <v>0.48234615880055182</v>
+        <v>0.47961669851424948</v>
       </c>
       <c r="K15">
-        <v>0.47963717163904201</v>
+        <v>0.47783774384601141</v>
       </c>
       <c r="L15">
-        <v>0.46234448776645182</v>
+        <v>0.45671968656671758</v>
       </c>
       <c r="M15">
-        <v>0.4269398340551091</v>
+        <v>0.41960237073461842</v>
       </c>
       <c r="N15">
-        <v>0.4471611225452608</v>
+        <v>0.44473036064154953</v>
       </c>
       <c r="O15">
-        <v>0.472992471739547</v>
+        <v>0.46884475330171149</v>
       </c>
       <c r="P15">
-        <v>0.50101766262975911</v>
+        <v>0.49749119639339939</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1364,49 +1335,49 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>0.25045517953535729</v>
-      </c>
-      <c r="C16">
-        <v>0.35948291239604407</v>
+        <v>0.2477303371550926</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.35588945867578542</v>
       </c>
       <c r="D16">
-        <v>0.41753962477638801</v>
+        <v>0.41287751111218418</v>
       </c>
       <c r="E16">
-        <v>0.44848189822038631</v>
+        <v>0.44812019618050147</v>
       </c>
       <c r="F16">
-        <v>0.46141283476645673</v>
+        <v>0.46008128028202261</v>
       </c>
       <c r="G16">
-        <v>0.48756285763270879</v>
+        <v>0.48596661711998529</v>
       </c>
       <c r="H16">
-        <v>0.46551419670773631</v>
+        <v>0.46448840617249593</v>
       </c>
       <c r="I16">
-        <v>0.48266866877982001</v>
+        <v>0.4827706822783473</v>
       </c>
       <c r="J16">
-        <v>0.48312308789178149</v>
+        <v>0.48316273559314371</v>
       </c>
       <c r="K16">
-        <v>0.4814759492261152</v>
+        <v>0.48263460109655221</v>
       </c>
       <c r="L16">
-        <v>0.46583925493717587</v>
+        <v>0.46563056704204708</v>
       </c>
       <c r="M16">
-        <v>0.43954934299512372</v>
+        <v>0.42860174522250349</v>
       </c>
       <c r="N16">
-        <v>0.45799946873567748</v>
+        <v>0.45135216222488311</v>
       </c>
       <c r="O16">
-        <v>0.48242501471009602</v>
+        <v>0.48152828590457941</v>
       </c>
       <c r="P16">
-        <v>0.50966492716512013</v>
+        <v>0.50335438524722942</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1414,199 +1385,199 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>0.25049888688607719</v>
-      </c>
-      <c r="C17">
-        <v>0.3587301287111358</v>
+        <v>0.2495260357015264</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.35814200583286038</v>
       </c>
       <c r="D17">
-        <v>0.41320028396760983</v>
+        <v>0.41285385452949719</v>
       </c>
       <c r="E17">
-        <v>0.44420526890049988</v>
+        <v>0.44695529179041621</v>
       </c>
       <c r="F17">
-        <v>0.45600520473996409</v>
+        <v>0.45848941532021092</v>
       </c>
       <c r="G17">
-        <v>0.48749076407200909</v>
+        <v>0.4821236622718158</v>
       </c>
       <c r="H17">
-        <v>0.46224305037718599</v>
+        <v>0.46021333986661711</v>
       </c>
       <c r="I17">
-        <v>0.48309623055829742</v>
+        <v>0.4791204977016531</v>
       </c>
       <c r="J17">
-        <v>0.48465135105318291</v>
+        <v>0.47994374508380239</v>
       </c>
       <c r="K17">
-        <v>0.48233182769711569</v>
+        <v>0.47962350917066943</v>
       </c>
       <c r="L17">
-        <v>0.46105659558462347</v>
+        <v>0.45665664964935088</v>
       </c>
       <c r="M17">
-        <v>0.43154171404517161</v>
+        <v>0.42672374675626279</v>
       </c>
       <c r="N17">
-        <v>0.45644824991733912</v>
+        <v>0.44860826806263587</v>
       </c>
       <c r="O17">
-        <v>0.4827854145947264</v>
+        <v>0.47757381711234032</v>
       </c>
       <c r="P17">
-        <v>0.50895180741488866</v>
+        <v>0.50116920326476722</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="B18">
-        <v>0.3829206244797097</v>
+      <c r="B18" s="2">
+        <v>0.38373486156678371</v>
       </c>
       <c r="C18">
-        <v>0.38787026000961861</v>
+        <v>0.38462301801476578</v>
       </c>
       <c r="D18">
-        <v>0.38531917253944742</v>
+        <v>0.38027805464217851</v>
       </c>
       <c r="E18">
-        <v>0.35231991233042942</v>
+        <v>0.34378182633721838</v>
       </c>
       <c r="F18">
-        <v>0.3818769707081755</v>
+        <v>0.37275797102886582</v>
       </c>
       <c r="G18">
-        <v>0.34856293405878308</v>
+        <v>0.34572857779208821</v>
       </c>
       <c r="H18">
-        <v>0.40965110213123018</v>
+        <v>0.39663713100858911</v>
       </c>
       <c r="I18">
-        <v>0.45530696327941889</v>
+        <v>0.44527223376025837</v>
       </c>
       <c r="J18">
-        <v>0.48224897713946879</v>
+        <v>0.4745601947321928</v>
       </c>
       <c r="K18">
-        <v>0.49591558142414499</v>
+        <v>0.48910254486086291</v>
       </c>
       <c r="L18">
-        <v>0.4888255082060104</v>
+        <v>0.48176791819911241</v>
       </c>
       <c r="M18">
-        <v>0.49067716173132692</v>
+        <v>0.48127448606235212</v>
       </c>
       <c r="N18">
-        <v>0.47139526891517147</v>
+        <v>0.45973914006765793</v>
       </c>
       <c r="O18">
-        <v>0.46683308200442353</v>
+        <v>0.45232631712331772</v>
       </c>
       <c r="P18">
-        <v>0.45741608944476819</v>
+        <v>0.44858265166198541</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B19">
-        <v>0.38232680388022378</v>
+      <c r="B19" s="2">
+        <v>0.38335311966087771</v>
       </c>
       <c r="C19">
-        <v>0.39229327733819941</v>
+        <v>0.3938189935590658</v>
       </c>
       <c r="D19">
-        <v>0.39372550436419418</v>
+        <v>0.39658363462535268</v>
       </c>
       <c r="E19">
-        <v>0.30041008981099648</v>
+        <v>0.29967221182624898</v>
       </c>
       <c r="F19">
-        <v>0.35756033407064852</v>
+        <v>0.34879866464518577</v>
       </c>
       <c r="G19">
-        <v>0.37697163539546508</v>
+        <v>0.37130651959800809</v>
       </c>
       <c r="H19">
-        <v>0.46042311383558648</v>
+        <v>0.45412419176090818</v>
       </c>
       <c r="I19">
-        <v>0.46449619732140818</v>
+        <v>0.45998001620194151</v>
       </c>
       <c r="J19">
-        <v>0.50487449081605795</v>
+        <v>0.50007787946014892</v>
       </c>
       <c r="K19">
-        <v>0.51126897129209725</v>
+        <v>0.5061844618969672</v>
       </c>
       <c r="L19">
-        <v>0.49030169894814479</v>
+        <v>0.48568993935431731</v>
       </c>
       <c r="M19">
-        <v>0.48335817300096351</v>
+        <v>0.47945983937772652</v>
       </c>
       <c r="N19">
-        <v>0.48276645248896238</v>
+        <v>0.48548749439723848</v>
       </c>
       <c r="O19">
-        <v>0.48005061972259588</v>
+        <v>0.48156150518387753</v>
       </c>
       <c r="P19">
-        <v>0.48920386549547179</v>
+        <v>0.49689998246942241</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B20">
-        <v>0.38221038325820422</v>
+      <c r="B20" s="2">
+        <v>0.3802690801944737</v>
       </c>
       <c r="C20">
-        <v>0.39089993633443149</v>
+        <v>0.38946175240662417</v>
       </c>
       <c r="D20">
-        <v>0.3917979792076528</v>
+        <v>0.39012910321864658</v>
       </c>
       <c r="E20">
-        <v>0.37238384808865982</v>
+        <v>0.36809486660150281</v>
       </c>
       <c r="F20">
-        <v>0.35967289563407639</v>
+        <v>0.34684873220119328</v>
       </c>
       <c r="G20">
-        <v>0.38102124486522509</v>
+        <v>0.36842934334863969</v>
       </c>
       <c r="H20">
-        <v>0.44896039535528381</v>
+        <v>0.43711763145435589</v>
       </c>
       <c r="I20">
-        <v>0.50153834822739896</v>
+        <v>0.48805520488673798</v>
       </c>
       <c r="J20">
-        <v>0.53118762404585362</v>
+        <v>0.51469650902848296</v>
       </c>
       <c r="K20">
-        <v>0.5088513124276457</v>
+        <v>0.49362431466490703</v>
       </c>
       <c r="L20">
-        <v>0.49773268751606548</v>
+        <v>0.47634812889056161</v>
       </c>
       <c r="M20">
-        <v>0.48362140345412141</v>
+        <v>0.46258375780261451</v>
       </c>
       <c r="N20">
-        <v>0.47605555628649637</v>
+        <v>0.46073067508659088</v>
       </c>
       <c r="O20">
-        <v>0.49557153660481662</v>
+        <v>0.48922138632268991</v>
       </c>
       <c r="P20">
-        <v>0.50164886885171989</v>
+        <v>0.4953842694316653</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1614,49 +1585,49 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>0.29278673137342381</v>
+        <v>0.29332305815037291</v>
       </c>
       <c r="C21">
-        <v>0.38420554968684623</v>
+        <v>0.38409662544220119</v>
       </c>
       <c r="D21">
-        <v>0.39810422728965111</v>
+        <v>0.40091208529526617</v>
       </c>
       <c r="E21">
-        <v>0.40999711367311598</v>
+        <v>0.41185455037350682</v>
       </c>
       <c r="F21">
-        <v>0.37475401199669678</v>
+        <v>0.38277279774314749</v>
       </c>
       <c r="G21">
-        <v>0.39246499732857371</v>
+        <v>0.40343525143556491</v>
       </c>
       <c r="H21">
-        <v>0.35205673512560559</v>
+        <v>0.3658249087938783</v>
       </c>
       <c r="I21">
-        <v>0.35217383871523</v>
+        <v>0.37182965120172301</v>
       </c>
       <c r="J21">
-        <v>0.35895148768775292</v>
+        <v>0.37499066223125699</v>
       </c>
       <c r="K21">
-        <v>0.33676684961256859</v>
+        <v>0.34852438225478072</v>
       </c>
       <c r="L21">
-        <v>0.29399486790207652</v>
+        <v>0.30712230415953717</v>
       </c>
       <c r="M21">
-        <v>0.27737004916327518</v>
+        <v>0.285937871701195</v>
       </c>
       <c r="N21">
-        <v>0.2247239528839427</v>
+        <v>0.2306889402046437</v>
       </c>
       <c r="O21">
-        <v>0.1932266555546408</v>
+        <v>0.19361301516336241</v>
       </c>
       <c r="P21">
-        <v>0.17970034661005979</v>
+        <v>0.17707550971906891</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1664,49 +1635,49 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>0.29328308446453621</v>
+        <v>0.29312974070869119</v>
       </c>
       <c r="C22">
-        <v>0.3842250214721088</v>
+        <v>0.38512965171687891</v>
       </c>
       <c r="D22">
-        <v>0.40176081187606821</v>
+        <v>0.40087419664445112</v>
       </c>
       <c r="E22">
-        <v>0.40917523354367791</v>
+        <v>0.40900844421800331</v>
       </c>
       <c r="F22">
-        <v>0.38885499819311309</v>
+        <v>0.38204344400492679</v>
       </c>
       <c r="G22">
-        <v>0.40581171833361912</v>
+        <v>0.4022388186326345</v>
       </c>
       <c r="H22">
-        <v>0.35978006019680109</v>
+        <v>0.35206414542810488</v>
       </c>
       <c r="I22">
-        <v>0.3493515214726548</v>
+        <v>0.34445393516943101</v>
       </c>
       <c r="J22">
-        <v>0.35365799700256739</v>
+        <v>0.35362680193294871</v>
       </c>
       <c r="K22">
-        <v>0.33835940194713171</v>
+        <v>0.33249362687504952</v>
       </c>
       <c r="L22">
-        <v>0.29579005186148499</v>
+        <v>0.29734800300000491</v>
       </c>
       <c r="M22">
-        <v>0.28238234937140139</v>
+        <v>0.28530897472072542</v>
       </c>
       <c r="N22">
-        <v>0.23909194029340611</v>
+        <v>0.25063242444980971</v>
       </c>
       <c r="O22">
-        <v>0.20096896670415049</v>
+        <v>0.20300320312280071</v>
       </c>
       <c r="P22">
-        <v>0.19199213653501429</v>
+        <v>0.1918192438599928</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -1714,49 +1685,49 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>0.38240257886962331</v>
+        <v>0.38385460037954561</v>
       </c>
       <c r="C23">
-        <v>0.29971204374888383</v>
+        <v>0.29784388260831057</v>
       </c>
       <c r="D23">
-        <v>0.34520012719147708</v>
+        <v>0.34132289720987052</v>
       </c>
       <c r="E23">
-        <v>0.38996803710021871</v>
+        <v>0.38450868688839751</v>
       </c>
       <c r="F23">
-        <v>0.3901960174664903</v>
+        <v>0.38647684031817531</v>
       </c>
       <c r="G23">
-        <v>0.39897795158376381</v>
+        <v>0.40173113245711911</v>
       </c>
       <c r="H23">
-        <v>0.37218148936211709</v>
+        <v>0.37862388131725161</v>
       </c>
       <c r="I23">
-        <v>0.36512142206913079</v>
+        <v>0.36723094412180068</v>
       </c>
       <c r="J23">
-        <v>0.32633703851487073</v>
+        <v>0.32986590013112821</v>
       </c>
       <c r="K23">
-        <v>0.30620595396785483</v>
+        <v>0.30834712029215799</v>
       </c>
       <c r="L23">
-        <v>0.27984986647644911</v>
+        <v>0.28204395880469951</v>
       </c>
       <c r="M23">
-        <v>0.28697824140652511</v>
+        <v>0.28663155310299349</v>
       </c>
       <c r="N23">
-        <v>0.27755318114200173</v>
+        <v>0.28176863299534338</v>
       </c>
       <c r="O23">
-        <v>0.26330055071937258</v>
+        <v>0.27103977559068182</v>
       </c>
       <c r="P23">
-        <v>0.23462440911934129</v>
+        <v>0.24495640353389689</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1764,49 +1735,49 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>1.40098378722349E-2</v>
+        <v>1.145249591600791E-2</v>
       </c>
       <c r="C24">
-        <v>-0.1165727887318007</v>
+        <v>-0.1231772731881617</v>
       </c>
       <c r="D24">
-        <v>-0.13164385519869781</v>
+        <v>-0.13881686592372219</v>
       </c>
       <c r="E24">
-        <v>-0.18909790281178721</v>
+        <v>-0.1848223997237729</v>
       </c>
       <c r="F24">
-        <v>-0.34312204723603001</v>
+        <v>-0.34586556077331337</v>
       </c>
       <c r="G24">
-        <v>-0.35018834240893421</v>
+        <v>-0.34296413750221738</v>
       </c>
       <c r="H24">
-        <v>-0.34477771268787583</v>
+        <v>-0.33148502201187291</v>
       </c>
       <c r="I24">
-        <v>-0.39186471003098838</v>
+        <v>-0.38413585775515591</v>
       </c>
       <c r="J24">
-        <v>-0.46574855136314569</v>
+        <v>-0.4508393108160636</v>
       </c>
       <c r="K24">
-        <v>-0.61725786617345524</v>
+        <v>-0.60014231121493911</v>
       </c>
       <c r="L24">
-        <v>-0.61027189929117753</v>
+        <v>-0.59095295660357572</v>
       </c>
       <c r="M24">
-        <v>-0.54635889402307369</v>
+        <v>-0.54518267027280343</v>
       </c>
       <c r="N24">
-        <v>-0.50024935441000251</v>
+        <v>-0.49153397560795947</v>
       </c>
       <c r="O24">
-        <v>-0.45961399060399499</v>
+        <v>-0.44986287799899932</v>
       </c>
       <c r="P24">
-        <v>-0.45063455799203472</v>
+        <v>-0.43605079507461619</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -1814,49 +1785,49 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <v>-5.3992842380858911E-3</v>
+        <v>-4.2156463013841997E-3</v>
       </c>
       <c r="C25">
-        <v>-0.12079579496964971</v>
+        <v>-0.11895412189300229</v>
       </c>
       <c r="D25">
-        <v>-0.17240539494559889</v>
+        <v>-0.16838918486031729</v>
       </c>
       <c r="E25">
-        <v>-0.33578885493596261</v>
+        <v>-0.33311900795502741</v>
       </c>
       <c r="F25">
-        <v>-0.34350328723088969</v>
+        <v>-0.34307439724185262</v>
       </c>
       <c r="G25">
-        <v>-0.44409485218873451</v>
+        <v>-0.44755876769859793</v>
       </c>
       <c r="H25">
-        <v>-0.63823365039975077</v>
+        <v>-0.65077597588349567</v>
       </c>
       <c r="I25">
-        <v>-0.73790253289573615</v>
+        <v>-0.74971973257113877</v>
       </c>
       <c r="J25">
-        <v>-0.67590794282877453</v>
+        <v>-0.68848934033894482</v>
       </c>
       <c r="K25">
-        <v>-0.71216742306488356</v>
+        <v>-0.72695542150444636</v>
       </c>
       <c r="L25">
-        <v>-0.76174979477248117</v>
+        <v>-0.7875040065329677</v>
       </c>
       <c r="M25">
-        <v>-0.8566171502669816</v>
+        <v>-0.88789330359486429</v>
       </c>
       <c r="N25">
-        <v>-0.93541778533663811</v>
+        <v>-0.97059950806978734</v>
       </c>
       <c r="O25">
-        <v>-0.90804185334139487</v>
+        <v>-0.93182686323477193</v>
       </c>
       <c r="P25">
-        <v>-0.89858380091531775</v>
+        <v>-0.91974767988889061</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1864,49 +1835,49 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>1.0786714646571331E-2</v>
+        <v>1.3499371161112699E-2</v>
       </c>
       <c r="C26">
-        <v>-5.2794601252647289E-2</v>
+        <v>-4.3227899516354577E-2</v>
       </c>
       <c r="D26">
-        <v>-5.840120630228901E-2</v>
+        <v>-4.8983857734805132E-2</v>
       </c>
       <c r="E26">
-        <v>-0.17144561568817571</v>
+        <v>-0.15790497228934011</v>
       </c>
       <c r="F26">
-        <v>-0.23130726731618481</v>
+        <v>-0.21466833542978259</v>
       </c>
       <c r="G26">
-        <v>-0.17385657392575271</v>
+        <v>-0.16430472445202909</v>
       </c>
       <c r="H26">
-        <v>-0.1314423645382212</v>
+        <v>-0.12380937750226161</v>
       </c>
       <c r="I26">
-        <v>-0.16727493426047341</v>
+        <v>-0.14194548495656251</v>
       </c>
       <c r="J26">
-        <v>-0.1515410584948404</v>
+        <v>-0.14120074186041839</v>
       </c>
       <c r="K26">
-        <v>-9.2309119251039462E-2</v>
+        <v>-6.8592686971046535E-2</v>
       </c>
       <c r="L26">
-        <v>-0.2726309787946421</v>
+        <v>-0.24945480383465299</v>
       </c>
       <c r="M26">
-        <v>-0.37228782252231668</v>
+        <v>-0.3438511963575826</v>
       </c>
       <c r="N26">
-        <v>-0.354025904542068</v>
+        <v>-0.32965400250926269</v>
       </c>
       <c r="O26">
-        <v>-0.40396703814044682</v>
+        <v>-0.38542210265372912</v>
       </c>
       <c r="P26">
-        <v>-0.44750268576256752</v>
+        <v>-0.41328056450334882</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1914,49 +1885,49 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>1.0757079332132951E-2</v>
+        <v>1.3359144263879189E-2</v>
       </c>
       <c r="C27">
-        <v>-1.668651177670771E-2</v>
+        <v>-1.340377944453354E-2</v>
       </c>
       <c r="D27">
-        <v>-0.27036226373965699</v>
+        <v>-0.25736203672223451</v>
       </c>
       <c r="E27">
-        <v>-0.1968512572446392</v>
+        <v>-0.1913604865401671</v>
       </c>
       <c r="F27">
-        <v>-0.1213451550068682</v>
+        <v>-0.1171785880590388</v>
       </c>
       <c r="G27">
-        <v>-0.1387759132952916</v>
+        <v>-0.1322758681461752</v>
       </c>
       <c r="H27">
-        <v>-0.1445716206560167</v>
+        <v>-0.1273916677934635</v>
       </c>
       <c r="I27">
-        <v>-7.962431654954108E-2</v>
+        <v>-6.9549870758506452E-2</v>
       </c>
       <c r="J27">
-        <v>-0.15792917186674629</v>
+        <v>-0.1567287588909389</v>
       </c>
       <c r="K27">
-        <v>-0.23400670849302929</v>
+        <v>-0.2358700408440132</v>
       </c>
       <c r="L27">
-        <v>-0.27456713456297932</v>
+        <v>-0.28444571292787968</v>
       </c>
       <c r="M27">
-        <v>-0.32544605670466581</v>
+        <v>-0.3339756142932086</v>
       </c>
       <c r="N27">
-        <v>-0.31976012037282198</v>
+        <v>-0.33327305331691731</v>
       </c>
       <c r="O27">
-        <v>-0.39939363030781128</v>
+        <v>-0.41852968588180839</v>
       </c>
       <c r="P27">
-        <v>-0.4510829366915326</v>
+        <v>-0.48109689058405342</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -1964,49 +1935,49 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>0.37071657314868273</v>
+        <v>0.37045965903778511</v>
       </c>
       <c r="C28">
-        <v>0.41194817147166068</v>
+        <v>0.41131530211772671</v>
       </c>
       <c r="D28">
-        <v>0.43526539928258279</v>
+        <v>0.43583280400466529</v>
       </c>
       <c r="E28">
-        <v>0.45768792564132649</v>
+        <v>0.45868753894111092</v>
       </c>
       <c r="F28">
-        <v>0.41339118128038382</v>
+        <v>0.41924447537992221</v>
       </c>
       <c r="G28">
-        <v>0.37364657504901061</v>
+        <v>0.38197767548190381</v>
       </c>
       <c r="H28">
-        <v>0.3381597824439822</v>
+        <v>0.34845198116105908</v>
       </c>
       <c r="I28">
-        <v>0.43433796514952588</v>
+        <v>0.44124889254067051</v>
       </c>
       <c r="J28">
-        <v>0.47973512239658189</v>
+        <v>0.48766532623335118</v>
       </c>
       <c r="K28">
-        <v>0.46907589805830169</v>
+        <v>0.46925222901319308</v>
       </c>
       <c r="L28">
-        <v>0.49582394624256271</v>
+        <v>0.49685776164297979</v>
       </c>
       <c r="M28">
-        <v>0.45753556942601348</v>
+        <v>0.45386362658286811</v>
       </c>
       <c r="N28">
-        <v>0.4557348178842221</v>
+        <v>0.45109316498183882</v>
       </c>
       <c r="O28">
-        <v>0.43545836665780241</v>
+        <v>0.43059987752313739</v>
       </c>
       <c r="P28">
-        <v>0.40117989037898583</v>
+        <v>0.40081366630514381</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2014,49 +1985,49 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>0.37044066777913259</v>
+        <v>0.36859859897067832</v>
       </c>
       <c r="C29">
-        <v>0.41408751200170452</v>
+        <v>0.40959240565631427</v>
       </c>
       <c r="D29">
-        <v>0.44132852825434321</v>
+        <v>0.43706192940361899</v>
       </c>
       <c r="E29">
-        <v>0.46694944422025958</v>
+        <v>0.46325484023511238</v>
       </c>
       <c r="F29">
-        <v>0.40932789891965249</v>
+        <v>0.40398152819659389</v>
       </c>
       <c r="G29">
-        <v>0.41772461510707948</v>
+        <v>0.40878020132588933</v>
       </c>
       <c r="H29">
-        <v>0.40660775833530849</v>
+        <v>0.39868093292388668</v>
       </c>
       <c r="I29">
-        <v>0.46191604615292498</v>
+        <v>0.45940743631644521</v>
       </c>
       <c r="J29">
-        <v>0.50601624626883357</v>
+        <v>0.50402235350015379</v>
       </c>
       <c r="K29">
-        <v>0.52478305038582018</v>
+        <v>0.51712172783789889</v>
       </c>
       <c r="L29">
-        <v>0.53211922561606628</v>
+        <v>0.53073846451905582</v>
       </c>
       <c r="M29">
-        <v>0.54223956610704105</v>
+        <v>0.53805717731684399</v>
       </c>
       <c r="N29">
-        <v>0.52816688769698339</v>
+        <v>0.52415740106340591</v>
       </c>
       <c r="O29">
-        <v>0.51093406240415529</v>
+        <v>0.50417516895077941</v>
       </c>
       <c r="P29">
-        <v>0.48315606831576652</v>
+        <v>0.47474726314848481</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2064,49 +2035,49 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>0.38059226919680839</v>
+        <v>0.38095702087491162</v>
       </c>
       <c r="C30">
-        <v>0.40269583415204258</v>
+        <v>0.40384411974891499</v>
       </c>
       <c r="D30">
-        <v>0.41187118012105189</v>
+        <v>0.41605619836810431</v>
       </c>
       <c r="E30">
-        <v>0.43525033634317523</v>
+        <v>0.4352329517588458</v>
       </c>
       <c r="F30">
-        <v>0.38992136546412592</v>
+        <v>0.39289966557688411</v>
       </c>
       <c r="G30">
-        <v>0.38695936427676869</v>
+        <v>0.37981493220787099</v>
       </c>
       <c r="H30">
-        <v>0.38771462436124388</v>
+        <v>0.37930113504857033</v>
       </c>
       <c r="I30">
-        <v>0.46122846980004012</v>
+        <v>0.45489463789359941</v>
       </c>
       <c r="J30">
-        <v>0.51349196029181554</v>
+        <v>0.50789824386339655</v>
       </c>
       <c r="K30">
-        <v>0.48380739338133188</v>
+        <v>0.48204436706357628</v>
       </c>
       <c r="L30">
-        <v>0.50159534338316003</v>
+        <v>0.50278390506291493</v>
       </c>
       <c r="M30">
-        <v>0.50650989734775209</v>
+        <v>0.50605393875022797</v>
       </c>
       <c r="N30">
-        <v>0.50183913189706897</v>
+        <v>0.49979809749506188</v>
       </c>
       <c r="O30">
-        <v>0.47895812561821721</v>
+        <v>0.47210892780685432</v>
       </c>
       <c r="P30">
-        <v>0.43631992299418509</v>
+        <v>0.42761105017450612</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2114,49 +2085,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>0.38189321260170622</v>
+        <v>0.38288864856871552</v>
       </c>
       <c r="C31">
-        <v>0.40351562515729578</v>
+        <v>0.40481973289056727</v>
       </c>
       <c r="D31">
-        <v>0.41369234852965592</v>
+        <v>0.41336024029010549</v>
       </c>
       <c r="E31">
-        <v>0.43582222506905388</v>
+        <v>0.44065904428130448</v>
       </c>
       <c r="F31">
-        <v>0.39989385845007852</v>
+        <v>0.39660164645292428</v>
       </c>
       <c r="G31">
-        <v>0.38965114615418178</v>
+        <v>0.38164407165349512</v>
       </c>
       <c r="H31">
-        <v>0.37867352552763961</v>
+        <v>0.37355260751527247</v>
       </c>
       <c r="I31">
-        <v>0.43851158060718348</v>
+        <v>0.44132269978455713</v>
       </c>
       <c r="J31">
-        <v>0.4989789229791215</v>
+        <v>0.50245410004861291</v>
       </c>
       <c r="K31">
-        <v>0.50009352647849492</v>
+        <v>0.49812094739078872</v>
       </c>
       <c r="L31">
-        <v>0.52449461490182203</v>
+        <v>0.51424534647636377</v>
       </c>
       <c r="M31">
-        <v>0.54137323112484137</v>
+        <v>0.52902551887758276</v>
       </c>
       <c r="N31">
-        <v>0.56467625296777035</v>
+        <v>0.55720047224203872</v>
       </c>
       <c r="O31">
-        <v>0.53953538483373087</v>
+        <v>0.53574538068271749</v>
       </c>
       <c r="P31">
-        <v>0.56135717065024981</v>
+        <v>0.55885066136020856</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2164,49 +2135,49 @@
         <v>46</v>
       </c>
       <c r="B32">
-        <v>0.37026439522389182</v>
+        <v>0.36982669924919659</v>
       </c>
       <c r="C32">
-        <v>0.41250259308414788</v>
+        <v>0.41051708056888081</v>
       </c>
       <c r="D32">
-        <v>0.4378430569060397</v>
+        <v>0.4359520477805004</v>
       </c>
       <c r="E32">
-        <v>0.4635975683114586</v>
+        <v>0.46219483840832482</v>
       </c>
       <c r="F32">
-        <v>0.41332913132262988</v>
+        <v>0.41233346784647318</v>
       </c>
       <c r="G32">
-        <v>0.41285968577295629</v>
+        <v>0.4157574002451323</v>
       </c>
       <c r="H32">
-        <v>0.40060100791784242</v>
+        <v>0.40131616249506241</v>
       </c>
       <c r="I32">
-        <v>0.44207130374615172</v>
+        <v>0.4403859413066748</v>
       </c>
       <c r="J32">
-        <v>0.48481012398404472</v>
+        <v>0.48157158079577839</v>
       </c>
       <c r="K32">
-        <v>0.51717398562185068</v>
+        <v>0.51618907119119728</v>
       </c>
       <c r="L32">
-        <v>0.53945569039223051</v>
+        <v>0.53556080591058364</v>
       </c>
       <c r="M32">
-        <v>0.55909347928626896</v>
+        <v>0.55523602238077008</v>
       </c>
       <c r="N32">
-        <v>0.54137692667965054</v>
+        <v>0.54019267502757184</v>
       </c>
       <c r="O32">
-        <v>0.55339956057936945</v>
+        <v>0.54862736276309865</v>
       </c>
       <c r="P32">
-        <v>0.5326360034632488</v>
+        <v>0.52853131523722363</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2214,49 +2185,49 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>0.36763966687782518</v>
+        <v>0.36820785851934779</v>
       </c>
       <c r="C33">
-        <v>0.40910244433198889</v>
+        <v>0.40922568397562092</v>
       </c>
       <c r="D33">
-        <v>0.43714063309213069</v>
+        <v>0.43608517856836132</v>
       </c>
       <c r="E33">
-        <v>0.46205170231280968</v>
+        <v>0.4629322214229426</v>
       </c>
       <c r="F33">
-        <v>0.41772844786059482</v>
+        <v>0.41382713051746589</v>
       </c>
       <c r="G33">
-        <v>0.42121991272408749</v>
+        <v>0.41835526394652373</v>
       </c>
       <c r="H33">
-        <v>0.41033809338648508</v>
+        <v>0.40596622874554211</v>
       </c>
       <c r="I33">
-        <v>0.45197276342870768</v>
+        <v>0.44756344516192431</v>
       </c>
       <c r="J33">
-        <v>0.49525549234019989</v>
+        <v>0.48469969545075542</v>
       </c>
       <c r="K33">
-        <v>0.52124813554744776</v>
+        <v>0.52089581641408778</v>
       </c>
       <c r="L33">
-        <v>0.5469449428272799</v>
-      </c>
-      <c r="M33" s="2">
-        <v>0.56572743041290496</v>
+        <v>0.54476421320998736</v>
+      </c>
+      <c r="M33">
+        <v>0.56397410354323241</v>
       </c>
       <c r="N33">
-        <v>0.55107958923010847</v>
+        <v>0.54509067441071735</v>
       </c>
       <c r="O33">
-        <v>0.55718327398082268</v>
+        <v>0.55477945741966894</v>
       </c>
       <c r="P33">
-        <v>0.53375850880758657</v>
+        <v>0.53041519026670481</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2264,49 +2235,49 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>0.36790307668206917</v>
+        <v>0.37230553964152918</v>
       </c>
       <c r="C34">
-        <v>0.41003905291638398</v>
+        <v>0.41411793710603662</v>
       </c>
       <c r="D34">
-        <v>0.43700048085250992</v>
+        <v>0.44186341744046481</v>
       </c>
       <c r="E34">
-        <v>0.46261330346972501</v>
+        <v>0.46551268443113297</v>
       </c>
       <c r="F34">
-        <v>0.41212915915858978</v>
+        <v>0.41255173431993042</v>
       </c>
       <c r="G34">
-        <v>0.40763092346033952</v>
+        <v>0.41698351332555539</v>
       </c>
       <c r="H34">
-        <v>0.40218210097307128</v>
+        <v>0.40301509434762389</v>
       </c>
       <c r="I34">
-        <v>0.4375257069577857</v>
+        <v>0.44357294436112649</v>
       </c>
       <c r="J34">
-        <v>0.48506046879518699</v>
+        <v>0.48705490460349082</v>
       </c>
       <c r="K34">
-        <v>0.515418306442465</v>
+        <v>0.520019973826924</v>
       </c>
       <c r="L34">
-        <v>0.53704635146132307</v>
+        <v>0.54310397591463533</v>
       </c>
       <c r="M34">
-        <v>0.55341376658431685</v>
+        <v>0.56238922815297843</v>
       </c>
       <c r="N34">
-        <v>0.53876348365757076</v>
+        <v>0.54660942761353482</v>
       </c>
       <c r="O34">
-        <v>0.54473539490095335</v>
+        <v>0.55253501028182983</v>
       </c>
       <c r="P34">
-        <v>0.52150710986893722</v>
+        <v>0.53329613494562322</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2314,49 +2285,49 @@
         <v>49</v>
       </c>
       <c r="B35">
-        <v>0.36570099923840638</v>
+        <v>0.36632229190693461</v>
       </c>
       <c r="C35">
-        <v>0.40779128059573427</v>
+        <v>0.40809650956113191</v>
       </c>
       <c r="D35">
-        <v>0.4338318733283808</v>
+        <v>0.43353215448548932</v>
       </c>
       <c r="E35">
-        <v>0.46050475749935332</v>
+        <v>0.46037851845004829</v>
       </c>
       <c r="F35">
-        <v>0.41134930395390329</v>
+        <v>0.4079490765047753</v>
       </c>
       <c r="G35">
-        <v>0.41187545309577639</v>
+        <v>0.40520406432252032</v>
       </c>
       <c r="H35">
-        <v>0.39725128129741388</v>
+        <v>0.39215555212327258</v>
       </c>
       <c r="I35">
-        <v>0.44037821665450821</v>
+        <v>0.43503482090479101</v>
       </c>
       <c r="J35">
-        <v>0.47874935515237982</v>
+        <v>0.46996719079089011</v>
       </c>
       <c r="K35">
-        <v>0.50145308349249784</v>
+        <v>0.50465244084073979</v>
       </c>
       <c r="L35">
-        <v>0.53247104574054693</v>
+        <v>0.53148032238610299</v>
       </c>
       <c r="M35">
-        <v>0.55268915954444342</v>
+        <v>0.55110362501044963</v>
       </c>
       <c r="N35">
-        <v>0.53887007879677873</v>
+        <v>0.53302101391217349</v>
       </c>
       <c r="O35">
-        <v>0.54577910638338745</v>
+        <v>0.54133763622742315</v>
       </c>
       <c r="P35">
-        <v>0.53089926320278247</v>
+        <v>0.52094703123028263</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2364,49 +2335,49 @@
         <v>50</v>
       </c>
       <c r="B36">
-        <v>0.37022287923004848</v>
+        <v>0.37172355871279761</v>
       </c>
       <c r="C36">
-        <v>0.41249370495013488</v>
+        <v>0.41430340602558352</v>
       </c>
       <c r="D36">
-        <v>0.44103271163640761</v>
+        <v>0.44154044795119762</v>
       </c>
       <c r="E36">
-        <v>0.46523218372586889</v>
+        <v>0.46691900134990189</v>
       </c>
       <c r="F36">
-        <v>0.41236596950788629</v>
+        <v>0.4162815138715138</v>
       </c>
       <c r="G36">
-        <v>0.4140044950556056</v>
+        <v>0.42007854215468199</v>
       </c>
       <c r="H36">
-        <v>0.40113996882468972</v>
+        <v>0.40877178957875998</v>
       </c>
       <c r="I36">
-        <v>0.44555143893218302</v>
+        <v>0.45175109031098232</v>
       </c>
       <c r="J36">
-        <v>0.47900428779883503</v>
+        <v>0.48941985475572403</v>
       </c>
       <c r="K36">
-        <v>0.50652209539499116</v>
+        <v>0.51167372956567925</v>
       </c>
       <c r="L36">
-        <v>0.52535903003274464</v>
+        <v>0.53543885614060682</v>
       </c>
       <c r="M36">
-        <v>0.54043828077895906</v>
+        <v>0.54867953746478482</v>
       </c>
       <c r="N36">
-        <v>0.52493557565927917</v>
+        <v>0.53111783165550686</v>
       </c>
       <c r="O36">
-        <v>0.53206293748082423</v>
+        <v>0.54128510067952018</v>
       </c>
       <c r="P36">
-        <v>0.5097161683036352</v>
+        <v>0.51857757086070533</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2414,49 +2385,49 @@
         <v>51</v>
       </c>
       <c r="B37">
-        <v>0.36665347183045632</v>
+        <v>0.36785093860868662</v>
       </c>
       <c r="C37">
-        <v>0.41032453562976412</v>
+        <v>0.40639135644671781</v>
       </c>
       <c r="D37">
-        <v>0.43499621625343571</v>
+        <v>0.43125985077334622</v>
       </c>
       <c r="E37">
-        <v>0.46183590130117091</v>
+        <v>0.45926802877968093</v>
       </c>
       <c r="F37">
-        <v>0.41100685856348362</v>
+        <v>0.40594276710181548</v>
       </c>
       <c r="G37">
-        <v>0.41052146397068551</v>
+        <v>0.41269718685917223</v>
       </c>
       <c r="H37">
-        <v>0.39409240529677192</v>
+        <v>0.3982886378636975</v>
       </c>
       <c r="I37">
-        <v>0.44408771838641392</v>
+        <v>0.44154139113220331</v>
       </c>
       <c r="J37">
-        <v>0.48592537920904189</v>
+        <v>0.47405045314718652</v>
       </c>
       <c r="K37">
-        <v>0.51026602433511659</v>
+        <v>0.50635431843994316</v>
       </c>
       <c r="L37">
-        <v>0.52962912088855763</v>
+        <v>0.52652178027713237</v>
       </c>
       <c r="M37">
-        <v>0.54627819278181622</v>
+        <v>0.54442712405845683</v>
       </c>
       <c r="N37">
-        <v>0.53358633225063201</v>
+        <v>0.53316357675040349</v>
       </c>
       <c r="O37">
-        <v>0.54181695384506479</v>
+        <v>0.54171300953423174</v>
       </c>
       <c r="P37">
-        <v>0.51450708940323253</v>
+        <v>0.51332675423492757</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -2464,49 +2435,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>0.36860516271927629</v>
+        <v>0.36571291537063172</v>
       </c>
       <c r="C38">
-        <v>0.4125476230752278</v>
+        <v>0.40959180408137619</v>
       </c>
       <c r="D38">
-        <v>0.44225770575777928</v>
+        <v>0.43712702899841538</v>
       </c>
       <c r="E38">
-        <v>0.46763037404849728</v>
+        <v>0.4634820034345884</v>
       </c>
       <c r="F38">
-        <v>0.42121349146783732</v>
+        <v>0.41733851443208669</v>
       </c>
       <c r="G38">
-        <v>0.42670288097434922</v>
+        <v>0.42121374491983649</v>
       </c>
       <c r="H38">
-        <v>0.41646643275515749</v>
+        <v>0.40639946164424151</v>
       </c>
       <c r="I38">
-        <v>0.46004572364696661</v>
+        <v>0.45069713989807592</v>
       </c>
       <c r="J38">
-        <v>0.49289314294978143</v>
+        <v>0.49694244835453222</v>
       </c>
       <c r="K38">
-        <v>0.52264895761666719</v>
+        <v>0.51478453858644324</v>
       </c>
       <c r="L38">
-        <v>0.54363774981196489</v>
+        <v>0.53639681517574644</v>
       </c>
       <c r="M38">
-        <v>0.56054489517224582</v>
+        <v>0.55408552118041843</v>
       </c>
       <c r="N38">
-        <v>0.5496022254163585</v>
+        <v>0.54651894675823698</v>
       </c>
       <c r="O38">
-        <v>0.55654394315095435</v>
+        <v>0.55441814650612298</v>
       </c>
       <c r="P38">
-        <v>0.52996453478525918</v>
+        <v>0.52698842637494192</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -2514,49 +2485,49 @@
         <v>53</v>
       </c>
       <c r="B39">
-        <v>0.36947830157327483</v>
+        <v>0.36973067468612608</v>
       </c>
       <c r="C39">
-        <v>0.4102509945147102</v>
+        <v>0.41339382534258018</v>
       </c>
       <c r="D39">
-        <v>0.43467388952390612</v>
+        <v>0.43989535209827618</v>
       </c>
       <c r="E39">
-        <v>0.46217835287159631</v>
+        <v>0.46546743921637052</v>
       </c>
       <c r="F39">
-        <v>0.41177642085295307</v>
+        <v>0.42030361895662149</v>
       </c>
       <c r="G39">
-        <v>0.41039815626446302</v>
+        <v>0.42117345199563633</v>
       </c>
       <c r="H39">
-        <v>0.40082111702938739</v>
+        <v>0.4096078032678987</v>
       </c>
       <c r="I39">
-        <v>0.44089468709117557</v>
+        <v>0.45358569429262069</v>
       </c>
       <c r="J39">
-        <v>0.48456419966691988</v>
+        <v>0.48901915481706187</v>
       </c>
       <c r="K39">
-        <v>0.51046532851651349</v>
+        <v>0.51401183508448722</v>
       </c>
       <c r="L39">
-        <v>0.53658792318642223</v>
+        <v>0.53603111923735614</v>
       </c>
       <c r="M39">
-        <v>0.55438984683986636</v>
+        <v>0.55623318430810254</v>
       </c>
       <c r="N39">
-        <v>0.54109771707325816</v>
+        <v>0.54601867697345474</v>
       </c>
       <c r="O39">
-        <v>0.5520140936255219</v>
+        <v>0.55347218626276828</v>
       </c>
       <c r="P39">
-        <v>0.52623850976333331</v>
+        <v>0.52539935993117926</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -2564,49 +2535,49 @@
         <v>54</v>
       </c>
       <c r="B40">
-        <v>0.36959280791720278</v>
+        <v>0.36855340971883471</v>
       </c>
       <c r="C40">
-        <v>0.41357247041315143</v>
+        <v>0.41126861519882751</v>
       </c>
       <c r="D40">
-        <v>0.44293988530872852</v>
+        <v>0.44177769940429062</v>
       </c>
       <c r="E40">
-        <v>0.46746966264914802</v>
+        <v>0.46753197431913918</v>
       </c>
       <c r="F40">
-        <v>0.41744246765044679</v>
+        <v>0.41702670778833312</v>
       </c>
       <c r="G40">
-        <v>0.42090383153182609</v>
+        <v>0.41950818367321802</v>
       </c>
       <c r="H40">
-        <v>0.41215236376325021</v>
+        <v>0.41025590049972482</v>
       </c>
       <c r="I40">
-        <v>0.4514977310633948</v>
+        <v>0.44770758061626897</v>
       </c>
       <c r="J40">
-        <v>0.48862220421904712</v>
+        <v>0.48525284389336559</v>
       </c>
       <c r="K40">
-        <v>0.51315532676677467</v>
+        <v>0.50581502107881493</v>
       </c>
       <c r="L40">
-        <v>0.54078929311801627</v>
+        <v>0.53755086996181733</v>
       </c>
       <c r="M40">
-        <v>0.55900436285168664</v>
+        <v>0.5571412106467436</v>
       </c>
       <c r="N40">
-        <v>0.54512437969692429</v>
+        <v>0.54649604932199936</v>
       </c>
       <c r="O40">
-        <v>0.55225844733909313</v>
+        <v>0.55830267275561452</v>
       </c>
       <c r="P40">
-        <v>0.52452296527269571</v>
+        <v>0.52811599253243091</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -2614,49 +2585,49 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>0.39081228994180411</v>
+        <v>0.38780545281483769</v>
       </c>
       <c r="C41">
-        <v>0.43215856629896432</v>
+        <v>0.42996170876584161</v>
       </c>
       <c r="D41">
-        <v>0.48439142822582348</v>
+        <v>0.48411981495518441</v>
       </c>
       <c r="E41">
-        <v>0.46541832347211831</v>
+        <v>0.46570021389045507</v>
       </c>
       <c r="F41">
-        <v>0.41162335073145961</v>
+        <v>0.40566658441795422</v>
       </c>
       <c r="G41">
-        <v>0.33103171866332881</v>
+        <v>0.3328000595160413</v>
       </c>
       <c r="H41">
-        <v>0.36543631789774772</v>
+        <v>0.36503634437005122</v>
       </c>
       <c r="I41">
-        <v>0.37681187851178782</v>
+        <v>0.37340735163466993</v>
       </c>
       <c r="J41">
-        <v>0.38455221807187479</v>
+        <v>0.38022543802443498</v>
       </c>
       <c r="K41">
-        <v>0.40874081933623202</v>
+        <v>0.40229110706056692</v>
       </c>
       <c r="L41">
-        <v>0.37583400997938149</v>
+        <v>0.36914632289270088</v>
       </c>
       <c r="M41">
-        <v>0.36476183023759479</v>
+        <v>0.36028806390435991</v>
       </c>
       <c r="N41">
-        <v>0.35497806448158281</v>
+        <v>0.34859642436066052</v>
       </c>
       <c r="O41">
-        <v>0.35016384825608687</v>
+        <v>0.34416781035013061</v>
       </c>
       <c r="P41">
-        <v>0.33788752149859652</v>
+        <v>0.33068225213212948</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -2664,49 +2635,49 @@
         <v>56</v>
       </c>
       <c r="B42">
-        <v>0.38944792078881968</v>
+        <v>0.39013413744865127</v>
       </c>
       <c r="C42">
-        <v>0.43545575320610252</v>
+        <v>0.42868431126181761</v>
       </c>
       <c r="D42">
-        <v>0.48323355177093519</v>
+        <v>0.47746941203292709</v>
       </c>
       <c r="E42">
-        <v>0.45839624770330428</v>
+        <v>0.44969005997803879</v>
       </c>
       <c r="F42">
-        <v>0.41158905590180828</v>
+        <v>0.40090704183284581</v>
       </c>
       <c r="G42">
-        <v>0.44495724334611608</v>
+        <v>0.43400984043551483</v>
       </c>
       <c r="H42">
-        <v>0.47559876358670639</v>
+        <v>0.46540943080396102</v>
       </c>
       <c r="I42">
-        <v>0.48088089744506662</v>
+        <v>0.47786786684531429</v>
       </c>
       <c r="J42">
-        <v>0.47726686530303652</v>
+        <v>0.47415443967791132</v>
       </c>
       <c r="K42">
-        <v>0.50731429567945896</v>
+        <v>0.50448559120681014</v>
       </c>
       <c r="L42">
-        <v>0.50321988979510801</v>
+        <v>0.50711872257774115</v>
       </c>
       <c r="M42">
-        <v>0.53641386306101346</v>
+        <v>0.5404778108302517</v>
       </c>
       <c r="N42">
-        <v>0.55731651162965212</v>
+        <v>0.56310715414468104</v>
       </c>
       <c r="O42">
-        <v>0.56458195892084995</v>
+        <v>0.57633866042889637</v>
       </c>
       <c r="P42">
-        <v>0.55106029476742902</v>
+        <v>0.56067000840906056</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -2714,49 +2685,49 @@
         <v>57</v>
       </c>
       <c r="B43">
-        <v>0.39322652174949668</v>
+        <v>0.39045721632695451</v>
       </c>
       <c r="C43">
-        <v>0.4344368242665313</v>
+        <v>0.42639065803821441</v>
       </c>
       <c r="D43">
-        <v>0.48170603706907511</v>
+        <v>0.4788221396086435</v>
       </c>
       <c r="E43">
-        <v>0.45548251099309112</v>
+        <v>0.45128285230632492</v>
       </c>
       <c r="F43">
-        <v>0.40858896383813831</v>
+        <v>0.40536701410840692</v>
       </c>
       <c r="G43">
-        <v>0.45109541631086941</v>
+        <v>0.45055045995012521</v>
       </c>
       <c r="H43">
-        <v>0.48738489504155119</v>
+        <v>0.48809315732140979</v>
       </c>
       <c r="I43">
-        <v>0.4776692811110404</v>
+        <v>0.47753931879324119</v>
       </c>
       <c r="J43">
-        <v>0.49236636005471979</v>
+        <v>0.49485448809746901</v>
       </c>
       <c r="K43">
-        <v>0.52236843083274387</v>
+        <v>0.52422764467194216</v>
       </c>
       <c r="L43">
-        <v>0.5132858365640125</v>
+        <v>0.51650664298636828</v>
       </c>
       <c r="M43">
-        <v>0.54964822505428912</v>
+        <v>0.55643865763280698</v>
       </c>
       <c r="N43">
-        <v>0.55745454275908768</v>
+        <v>0.56214211260455449</v>
       </c>
       <c r="O43">
-        <v>0.56693086855816022</v>
+        <v>0.57351923357560475</v>
       </c>
       <c r="P43">
-        <v>0.55582269925160155</v>
+        <v>0.56474339489053038</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -2764,49 +2735,49 @@
         <v>58</v>
       </c>
       <c r="B44">
-        <v>0.36736185203724891</v>
+        <v>0.36898654942831721</v>
       </c>
       <c r="C44">
-        <v>0.37754751538288012</v>
+        <v>0.37659693745130268</v>
       </c>
       <c r="D44">
-        <v>0.43809700212205532</v>
+        <v>0.43979815257851262</v>
       </c>
       <c r="E44">
-        <v>0.44470731145361281</v>
+        <v>0.44780904211092709</v>
       </c>
       <c r="F44">
-        <v>0.44246108794411448</v>
+        <v>0.44589770956545621</v>
       </c>
       <c r="G44">
-        <v>0.47293917747581748</v>
+        <v>0.47556187187550542</v>
       </c>
       <c r="H44">
-        <v>0.46766324634062678</v>
+        <v>0.4704896776748953</v>
       </c>
       <c r="I44">
-        <v>0.46034019872856519</v>
+        <v>0.46671716800146462</v>
       </c>
       <c r="J44">
-        <v>0.44526426485159981</v>
+        <v>0.45672325211775522</v>
       </c>
       <c r="K44">
-        <v>0.42785098682813438</v>
+        <v>0.4375567657442585</v>
       </c>
       <c r="L44">
-        <v>0.43736027195736438</v>
+        <v>0.4493995260308406</v>
       </c>
       <c r="M44">
-        <v>0.43048227330651478</v>
+        <v>0.44263720632796077</v>
       </c>
       <c r="N44">
-        <v>0.43010896698556278</v>
+        <v>0.43881827378059862</v>
       </c>
       <c r="O44">
-        <v>0.41299109554269869</v>
+        <v>0.42061530939657199</v>
       </c>
       <c r="P44">
-        <v>0.36943176790744059</v>
+        <v>0.38073116448159372</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -2814,49 +2785,49 @@
         <v>59</v>
       </c>
       <c r="B45">
-        <v>0.36707725601005819</v>
+        <v>0.36939854230779351</v>
       </c>
       <c r="C45">
-        <v>0.40248930501120361</v>
+        <v>0.40704362912341241</v>
       </c>
       <c r="D45">
-        <v>0.4023679094628716</v>
+        <v>0.40901686412499721</v>
       </c>
       <c r="E45">
-        <v>0.3819475281932157</v>
+        <v>0.38663325304331869</v>
       </c>
       <c r="F45">
-        <v>0.35940109710924178</v>
+        <v>0.35910056123489931</v>
       </c>
       <c r="G45">
-        <v>0.32763792913489281</v>
+        <v>0.33303087742154908</v>
       </c>
       <c r="H45">
-        <v>0.31768968152762911</v>
+        <v>0.32401800072109532</v>
       </c>
       <c r="I45">
-        <v>0.31352522648898512</v>
+        <v>0.31991329903417531</v>
       </c>
       <c r="J45">
-        <v>0.30047943127365723</v>
+        <v>0.30744551102974249</v>
       </c>
       <c r="K45">
-        <v>0.23545063416017109</v>
+        <v>0.24075169843126329</v>
       </c>
       <c r="L45">
-        <v>0.2077136356897131</v>
+        <v>0.2099964537665355</v>
       </c>
       <c r="M45">
-        <v>0.19587780756759249</v>
+        <v>0.19665445285731301</v>
       </c>
       <c r="N45">
-        <v>0.15607457052402801</v>
+        <v>0.15599475707437679</v>
       </c>
       <c r="O45">
-        <v>0.14211508740658299</v>
+        <v>0.13016917541843881</v>
       </c>
       <c r="P45">
-        <v>0.16379598962861031</v>
+        <v>0.14881265928940099</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -2864,49 +2835,49 @@
         <v>60</v>
       </c>
       <c r="B46">
-        <v>0.28578302452355447</v>
+        <v>0.28325350589887471</v>
       </c>
       <c r="C46">
-        <v>0.38591485460934521</v>
+        <v>0.38424353308790438</v>
       </c>
       <c r="D46">
-        <v>0.38584749126635831</v>
+        <v>0.38652613590584017</v>
       </c>
       <c r="E46">
-        <v>0.35286808361256122</v>
+        <v>0.35464208730051022</v>
       </c>
       <c r="F46">
-        <v>0.30110399984260722</v>
+        <v>0.30306246639252682</v>
       </c>
       <c r="G46">
-        <v>0.31708198144677718</v>
+        <v>0.31635899099246872</v>
       </c>
       <c r="H46">
-        <v>0.35034030446066472</v>
+        <v>0.34290975491506709</v>
       </c>
       <c r="I46">
-        <v>0.33818312054660449</v>
+        <v>0.3304580764957637</v>
       </c>
       <c r="J46">
-        <v>0.25665073733682747</v>
+        <v>0.26264623288530559</v>
       </c>
       <c r="K46">
-        <v>0.22203102316680809</v>
+        <v>0.23166843924627431</v>
       </c>
       <c r="L46">
-        <v>0.20786100908308339</v>
+        <v>0.2141929895264581</v>
       </c>
       <c r="M46">
-        <v>0.1675953380614571</v>
+        <v>0.17400576079609051</v>
       </c>
       <c r="N46">
-        <v>0.13378363311060881</v>
+        <v>0.1482999234162152</v>
       </c>
       <c r="O46">
-        <v>0.1459601310411579</v>
+        <v>0.1613212797226049</v>
       </c>
       <c r="P46">
-        <v>0.15274550119354269</v>
+        <v>0.1730662618972649</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -2914,54 +2885,54 @@
         <v>61</v>
       </c>
       <c r="B47">
-        <v>0.38348129573716938</v>
+        <v>0.38429981691475762</v>
       </c>
       <c r="C47">
-        <v>0.39159835626416972</v>
+        <v>0.390532803043808</v>
       </c>
       <c r="D47">
-        <v>0.38525707743209991</v>
+        <v>0.38347172915661198</v>
       </c>
       <c r="E47">
-        <v>0.38226763918132162</v>
+        <v>0.38056878457831528</v>
       </c>
       <c r="F47">
-        <v>0.35125943812525939</v>
+        <v>0.35426118283676261</v>
       </c>
       <c r="G47">
-        <v>0.35575966373633883</v>
+        <v>0.35832017404432293</v>
       </c>
       <c r="H47">
-        <v>0.37162200761507791</v>
+        <v>0.37584531915980163</v>
       </c>
       <c r="I47">
-        <v>0.37742301640785109</v>
+        <v>0.37963513425090389</v>
       </c>
       <c r="J47">
-        <v>0.31479526342840097</v>
+        <v>0.31431380720077767</v>
       </c>
       <c r="K47">
-        <v>0.32649761377065423</v>
+        <v>0.31930197385208159</v>
       </c>
       <c r="L47">
-        <v>0.31832477662765601</v>
+        <v>0.30788226164829979</v>
       </c>
       <c r="M47">
-        <v>0.30356822495878399</v>
+        <v>0.29491384256783748</v>
       </c>
       <c r="N47">
-        <v>0.30303315795976993</v>
+        <v>0.29924022583628862</v>
       </c>
       <c r="O47">
-        <v>0.30236842531336322</v>
+        <v>0.29287479049026172</v>
       </c>
       <c r="P47">
-        <v>0.28815964858573351</v>
+        <v>0.28259567198980129</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P32 B34:P47 B33:L33 N33:P33">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="B2:P47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2971,7 +2942,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_ADJR2.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\trans.alpha.carotenes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -244,50 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -329,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -361,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -396,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -572,2377 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="14" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.23443226001683981</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.3630596967281467</v>
+        <v>0.2372859898453829</v>
       </c>
       <c r="D2">
-        <v>0.39420933268981989</v>
+        <v>0.3674800840746863</v>
       </c>
       <c r="E2">
-        <v>0.43434064896296232</v>
+        <v>0.3977510626722862</v>
       </c>
       <c r="F2">
-        <v>0.45161303785808488</v>
+        <v>0.4356579747263302</v>
       </c>
       <c r="G2">
-        <v>0.49558818561362061</v>
+        <v>0.4588087656823962</v>
       </c>
       <c r="H2">
-        <v>0.4982150515590385</v>
+        <v>0.5032936175351598</v>
       </c>
       <c r="I2">
-        <v>0.4827046326125467</v>
+        <v>0.5058315877592136</v>
       </c>
       <c r="J2">
-        <v>0.47016236860429922</v>
+        <v>0.4868625239255344</v>
       </c>
       <c r="K2">
-        <v>0.45723842629909173</v>
+        <v>0.4798830939715808</v>
       </c>
       <c r="L2">
-        <v>0.48388859315829452</v>
+        <v>0.4670402653367994</v>
       </c>
       <c r="M2">
-        <v>0.45416917061075451</v>
+        <v>0.4954550528620146</v>
       </c>
       <c r="N2">
-        <v>0.4659709914505018</v>
+        <v>0.4642792072539034</v>
       </c>
       <c r="O2">
-        <v>0.45453378580358372</v>
+        <v>0.4793263498388913</v>
       </c>
       <c r="P2">
-        <v>0.47241063118006349</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4707511149238594</v>
+      </c>
+      <c r="Q2">
+        <v>0.4836102356624508</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.29353238472880122</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>0.38687193316261109</v>
+        <v>0.2887880546588604</v>
       </c>
       <c r="D3">
-        <v>0.39733231735765218</v>
+        <v>0.3821299935982997</v>
       </c>
       <c r="E3">
-        <v>0.38376029136400031</v>
+        <v>0.3937019001491008</v>
       </c>
       <c r="F3">
-        <v>0.34740406742365548</v>
+        <v>0.392195064219673</v>
       </c>
       <c r="G3">
-        <v>0.3756694833442048</v>
+        <v>0.349850531985645</v>
       </c>
       <c r="H3">
-        <v>0.34999677543213481</v>
+        <v>0.376237216403347</v>
       </c>
       <c r="I3">
-        <v>0.33330769352427808</v>
+        <v>0.346634786104164</v>
       </c>
       <c r="J3">
-        <v>0.33253638286536752</v>
+        <v>0.326942171344527</v>
       </c>
       <c r="K3">
-        <v>0.32876805217774591</v>
+        <v>0.3269026560342362</v>
       </c>
       <c r="L3">
-        <v>0.30002246948384959</v>
+        <v>0.3271616540883075</v>
       </c>
       <c r="M3">
-        <v>0.27399091103805778</v>
+        <v>0.2935122888984116</v>
       </c>
       <c r="N3">
-        <v>0.23647884334613459</v>
+        <v>0.2702995489921315</v>
       </c>
       <c r="O3">
-        <v>0.1968230250412554</v>
+        <v>0.231338902247176</v>
       </c>
       <c r="P3">
-        <v>0.1809183539949944</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.1859960995290226</v>
+      </c>
+      <c r="Q3">
+        <v>0.1669965696004942</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.25026553797456358</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>0.34224761827082029</v>
+        <v>0.2526972691167146</v>
       </c>
       <c r="D4">
-        <v>0.35454744075856159</v>
+        <v>0.3468895582030779</v>
       </c>
       <c r="E4">
-        <v>0.33571439610876541</v>
+        <v>0.3580083518056396</v>
       </c>
       <c r="F4">
-        <v>0.35449316123792868</v>
+        <v>0.3383767844092861</v>
       </c>
       <c r="G4">
-        <v>0.34427714197406561</v>
+        <v>0.3624396172673658</v>
       </c>
       <c r="H4">
-        <v>0.37589255177246877</v>
+        <v>0.3567060743609977</v>
       </c>
       <c r="I4">
-        <v>0.37556714728691049</v>
+        <v>0.3858066764769804</v>
       </c>
       <c r="J4">
-        <v>0.38217935313673812</v>
+        <v>0.3881713902516415</v>
       </c>
       <c r="K4">
-        <v>0.3325670083540283</v>
+        <v>0.3939262341889319</v>
       </c>
       <c r="L4">
-        <v>0.33219659004307078</v>
+        <v>0.344962021479254</v>
       </c>
       <c r="M4">
-        <v>0.34112662495125751</v>
+        <v>0.3399714591191709</v>
       </c>
       <c r="N4">
-        <v>0.36038946849715031</v>
+        <v>0.3517420560692094</v>
       </c>
       <c r="O4">
-        <v>0.34844290613413609</v>
+        <v>0.3699696702552124</v>
       </c>
       <c r="P4">
-        <v>0.31458411516062501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.3649269304571044</v>
+      </c>
+      <c r="Q4">
+        <v>0.3357306686443129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>0.37214729399021651</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>0.37525172072318058</v>
+        <v>0.3706029192772895</v>
       </c>
       <c r="D5">
-        <v>0.37658097199594059</v>
+        <v>0.3707557674590344</v>
       </c>
       <c r="E5">
-        <v>0.34356113839716268</v>
+        <v>0.3715415244751076</v>
       </c>
       <c r="F5">
-        <v>0.33925646888910188</v>
+        <v>0.335859913921336</v>
       </c>
       <c r="G5">
-        <v>0.31287654579736562</v>
+        <v>0.3359304260959673</v>
       </c>
       <c r="H5">
-        <v>0.31474712716744491</v>
+        <v>0.3208301621251913</v>
       </c>
       <c r="I5">
-        <v>0.35619789623149872</v>
+        <v>0.3215001375904801</v>
       </c>
       <c r="J5">
-        <v>0.37563615703787762</v>
+        <v>0.3610943369592024</v>
       </c>
       <c r="K5">
-        <v>0.35744952560358267</v>
+        <v>0.3801301295992263</v>
       </c>
       <c r="L5">
-        <v>0.35222868904047783</v>
+        <v>0.3585481950138827</v>
       </c>
       <c r="M5">
-        <v>0.33466966214806942</v>
+        <v>0.3578725836543328</v>
       </c>
       <c r="N5">
-        <v>0.29900193205342612</v>
+        <v>0.3438098476662333</v>
       </c>
       <c r="O5">
-        <v>0.3066650490399358</v>
+        <v>0.3138503028422164</v>
       </c>
       <c r="P5">
-        <v>0.28568744555473891</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.3192636110497702</v>
+      </c>
+      <c r="Q5">
+        <v>0.3002104736632111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>0.37589567217220171</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>0.38623354450824471</v>
+        <v>0.3738083915860234</v>
       </c>
       <c r="D6">
-        <v>0.38823266164569331</v>
+        <v>0.3826229283088085</v>
       </c>
       <c r="E6">
-        <v>0.29971113931803772</v>
+        <v>0.3849374873407473</v>
       </c>
       <c r="F6">
-        <v>0.35073134942858469</v>
+        <v>0.2965933275353043</v>
       </c>
       <c r="G6">
-        <v>0.31319051116298557</v>
+        <v>0.3504563012984926</v>
       </c>
       <c r="H6">
-        <v>0.34839862028937701</v>
+        <v>0.3249453313305996</v>
       </c>
       <c r="I6">
-        <v>0.39358376490181751</v>
+        <v>0.3531213161740352</v>
       </c>
       <c r="J6">
-        <v>0.37803304711620761</v>
+        <v>0.3982315475933703</v>
       </c>
       <c r="K6">
-        <v>0.36358352227346852</v>
+        <v>0.3860404739259364</v>
       </c>
       <c r="L6">
-        <v>0.33891028268713369</v>
+        <v>0.369796734674128</v>
       </c>
       <c r="M6">
-        <v>0.31081918079435877</v>
+        <v>0.338900328422415</v>
       </c>
       <c r="N6">
-        <v>0.29945211133329602</v>
+        <v>0.3140302523437014</v>
       </c>
       <c r="O6">
-        <v>0.30020695080035548</v>
+        <v>0.3046325169128505</v>
       </c>
       <c r="P6">
-        <v>0.33233895914048922</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3029762840982317</v>
+      </c>
+      <c r="Q6">
+        <v>0.3354544228845746</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.25111563245403512</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>0.3610921640649904</v>
+        <v>0.2504104991417195</v>
       </c>
       <c r="D7">
-        <v>0.4170052628765426</v>
+        <v>0.3586085592542452</v>
       </c>
       <c r="E7">
-        <v>0.4511703684369725</v>
+        <v>0.4144315615287916</v>
       </c>
       <c r="F7">
-        <v>0.46360969053802631</v>
+        <v>0.4477420803162681</v>
       </c>
       <c r="G7">
-        <v>0.49142564058712512</v>
+        <v>0.4557998718964558</v>
       </c>
       <c r="H7">
-        <v>0.46319029049319282</v>
+        <v>0.4910239122971797</v>
       </c>
       <c r="I7">
-        <v>0.48807918836053532</v>
+        <v>0.4573000696623582</v>
       </c>
       <c r="J7">
-        <v>0.49445870885636273</v>
+        <v>0.4823842833710912</v>
       </c>
       <c r="K7">
-        <v>0.49223932815465887</v>
+        <v>0.4886174413125017</v>
       </c>
       <c r="L7">
-        <v>0.4815710226806218</v>
+        <v>0.491767851731177</v>
       </c>
       <c r="M7">
-        <v>0.46139128969495952</v>
+        <v>0.4821479421077608</v>
       </c>
       <c r="N7">
-        <v>0.48163820938522012</v>
+        <v>0.4615159392987944</v>
       </c>
       <c r="O7">
-        <v>0.50110382104943985</v>
+        <v>0.482839037732461</v>
       </c>
       <c r="P7">
-        <v>0.49014058632648899</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.5032112143265195</v>
+      </c>
+      <c r="Q7">
+        <v>0.4941309729116479</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.29552871778744128</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>0.34105232914662159</v>
+        <v>0.2974942529044065</v>
       </c>
       <c r="D8">
-        <v>0.34223353507824622</v>
+        <v>0.3414132907185365</v>
       </c>
       <c r="E8">
-        <v>0.35889828836962251</v>
+        <v>0.3457006351516381</v>
       </c>
       <c r="F8">
-        <v>0.41198993559429531</v>
+        <v>0.3638297058899158</v>
       </c>
       <c r="G8">
-        <v>0.38217773759352958</v>
+        <v>0.4125848747626389</v>
       </c>
       <c r="H8">
-        <v>0.41855619153483931</v>
+        <v>0.384169812325317</v>
       </c>
       <c r="I8">
-        <v>0.43095183727945091</v>
+        <v>0.4183324948736096</v>
       </c>
       <c r="J8">
-        <v>0.40946782351457173</v>
+        <v>0.4352052232558427</v>
       </c>
       <c r="K8">
-        <v>0.40029182870197849</v>
+        <v>0.4127245632410537</v>
       </c>
       <c r="L8">
-        <v>0.39220198492496111</v>
+        <v>0.4011866376325741</v>
       </c>
       <c r="M8">
-        <v>0.40234022584104501</v>
+        <v>0.3948919978277956</v>
       </c>
       <c r="N8">
-        <v>0.4091309349918934</v>
+        <v>0.4021620485099048</v>
       </c>
       <c r="O8">
-        <v>0.40728752803009488</v>
+        <v>0.4163033518153014</v>
       </c>
       <c r="P8">
-        <v>0.38428415321944409</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4149348291299065</v>
+      </c>
+      <c r="Q8">
+        <v>0.3915951549023182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>0.2933052292351776</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>0.33717824959894233</v>
+        <v>0.294388375111144</v>
       </c>
       <c r="D9">
-        <v>0.33860091841515011</v>
+        <v>0.3408954685459297</v>
       </c>
       <c r="E9">
-        <v>0.35594565444380011</v>
+        <v>0.3458211925263504</v>
       </c>
       <c r="F9">
-        <v>0.40311144541242122</v>
+        <v>0.3626862547356449</v>
       </c>
       <c r="G9">
-        <v>0.3754011974981627</v>
+        <v>0.4126988488193994</v>
       </c>
       <c r="H9">
-        <v>0.4110534872957517</v>
+        <v>0.3866741952805136</v>
       </c>
       <c r="I9">
-        <v>0.42769479844041192</v>
+        <v>0.4235592502697906</v>
       </c>
       <c r="J9">
-        <v>0.41136392308359682</v>
+        <v>0.4360937123408979</v>
       </c>
       <c r="K9">
-        <v>0.39335715602424137</v>
+        <v>0.4214881994182332</v>
       </c>
       <c r="L9">
-        <v>0.3832009465473345</v>
+        <v>0.4050899265294662</v>
       </c>
       <c r="M9">
-        <v>0.3847653390167482</v>
+        <v>0.3905572990021167</v>
       </c>
       <c r="N9">
-        <v>0.40211532514905979</v>
+        <v>0.397047130984792</v>
       </c>
       <c r="O9">
-        <v>0.4311531914444896</v>
+        <v>0.4166531769075785</v>
       </c>
       <c r="P9">
-        <v>0.39786758766610097</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.4459203389251742</v>
+      </c>
+      <c r="Q9">
+        <v>0.4164554046363028</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>0.29404309696364789</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>0.33787331677511601</v>
+        <v>0.2954453387048752</v>
       </c>
       <c r="D10">
-        <v>0.34079349782344992</v>
+        <v>0.3412381018804087</v>
       </c>
       <c r="E10">
-        <v>0.35853764868921573</v>
+        <v>0.3483370911698564</v>
       </c>
       <c r="F10">
-        <v>0.40826924107930512</v>
+        <v>0.3661141235213251</v>
       </c>
       <c r="G10">
-        <v>0.37895758822489328</v>
+        <v>0.4080123163740272</v>
       </c>
       <c r="H10">
-        <v>0.41647859267879389</v>
+        <v>0.3879787539546355</v>
       </c>
       <c r="I10">
-        <v>0.43256694881923768</v>
+        <v>0.4201338947661254</v>
       </c>
       <c r="J10">
-        <v>0.41553017266310072</v>
+        <v>0.4341105874405933</v>
       </c>
       <c r="K10">
-        <v>0.39549620438988747</v>
+        <v>0.4172667036183446</v>
       </c>
       <c r="L10">
-        <v>0.38854236964838351</v>
+        <v>0.4032175880947105</v>
       </c>
       <c r="M10">
-        <v>0.39312861417965989</v>
+        <v>0.3925479294717742</v>
       </c>
       <c r="N10">
-        <v>0.41350679622723119</v>
+        <v>0.3989846915335618</v>
       </c>
       <c r="O10">
-        <v>0.44460623948698558</v>
+        <v>0.4208159482776284</v>
       </c>
       <c r="P10">
-        <v>0.41706492693156738</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.4497544133590389</v>
+      </c>
+      <c r="Q10">
+        <v>0.4160555026550671</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>0.29230423562794311</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>0.33926836877636563</v>
+        <v>0.2929826676529798</v>
       </c>
       <c r="D11">
-        <v>0.3465700021462349</v>
+        <v>0.3379149369166632</v>
       </c>
       <c r="E11">
-        <v>0.36461883404118561</v>
+        <v>0.338151373210335</v>
       </c>
       <c r="F11">
-        <v>0.40350085038877509</v>
+        <v>0.3524230747888495</v>
       </c>
       <c r="G11">
-        <v>0.38123458880904781</v>
+        <v>0.3932098511697494</v>
       </c>
       <c r="H11">
-        <v>0.41417241379099762</v>
+        <v>0.3663450461326013</v>
       </c>
       <c r="I11">
-        <v>0.42569958860489387</v>
+        <v>0.3989757888964425</v>
       </c>
       <c r="J11">
-        <v>0.41142887599083799</v>
+        <v>0.4169984774408007</v>
       </c>
       <c r="K11">
-        <v>0.38960446611955513</v>
+        <v>0.4033280125284672</v>
       </c>
       <c r="L11">
-        <v>0.37844836406472621</v>
+        <v>0.381480793948014</v>
       </c>
       <c r="M11">
-        <v>0.38343022566975188</v>
+        <v>0.3711428280178045</v>
       </c>
       <c r="N11">
-        <v>0.39363352049761929</v>
+        <v>0.3808250482194415</v>
       </c>
       <c r="O11">
-        <v>0.4076630607712774</v>
+        <v>0.3932912218390613</v>
       </c>
       <c r="P11">
-        <v>0.41493939929882567</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.4097318209293131</v>
+      </c>
+      <c r="Q11">
+        <v>0.413384212666661</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>0.37876921015099202</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>0.38087791976883167</v>
+        <v>0.3810656687199299</v>
       </c>
       <c r="D12">
-        <v>0.37789686424369517</v>
+        <v>0.3855856778293247</v>
       </c>
       <c r="E12">
-        <v>0.33391885208251759</v>
+        <v>0.383948213082462</v>
       </c>
       <c r="F12">
-        <v>0.34644237101610209</v>
+        <v>0.3440029726011451</v>
       </c>
       <c r="G12">
-        <v>0.35635111489939802</v>
+        <v>0.355459151327688</v>
       </c>
       <c r="H12">
-        <v>0.37554053283885169</v>
+        <v>0.365289206587006</v>
       </c>
       <c r="I12">
-        <v>0.42623720146346761</v>
+        <v>0.3843880869668144</v>
       </c>
       <c r="J12">
-        <v>0.43287570698733208</v>
+        <v>0.4386976217538549</v>
       </c>
       <c r="K12">
-        <v>0.43804929765824002</v>
+        <v>0.442637875407656</v>
       </c>
       <c r="L12">
-        <v>0.40553474694798303</v>
+        <v>0.4485485770492906</v>
       </c>
       <c r="M12">
-        <v>0.40285050616507601</v>
+        <v>0.4142096577667726</v>
       </c>
       <c r="N12">
-        <v>0.37134209118578781</v>
+        <v>0.4119693035186256</v>
       </c>
       <c r="O12">
-        <v>0.36621042512712709</v>
+        <v>0.3817890476677115</v>
       </c>
       <c r="P12">
-        <v>0.35960712493689811</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.3731182475325378</v>
+      </c>
+      <c r="Q12">
+        <v>0.3636599340217344</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.38270523475625801</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.40230962158880229</v>
+        <v>0.3825442699967501</v>
       </c>
       <c r="D13">
-        <v>0.4098632720542853</v>
+        <v>0.4029435198686834</v>
       </c>
       <c r="E13">
-        <v>0.40072457817242141</v>
+        <v>0.4087238850978739</v>
       </c>
       <c r="F13">
-        <v>0.35164896289084929</v>
+        <v>0.3971310083587521</v>
       </c>
       <c r="G13">
-        <v>0.33659607187056811</v>
+        <v>0.3482455924373858</v>
       </c>
       <c r="H13">
-        <v>0.3460472026165034</v>
+        <v>0.3353562258045975</v>
       </c>
       <c r="I13">
-        <v>0.37280355663993542</v>
+        <v>0.3419117312838457</v>
       </c>
       <c r="J13">
-        <v>0.37418237142171401</v>
+        <v>0.3651248500842519</v>
       </c>
       <c r="K13">
-        <v>0.37577325862268768</v>
+        <v>0.3690092462610711</v>
       </c>
       <c r="L13">
-        <v>0.38110062225578373</v>
+        <v>0.3695689691588024</v>
       </c>
       <c r="M13">
-        <v>0.3697876450735888</v>
+        <v>0.374347665419165</v>
       </c>
       <c r="N13">
-        <v>0.35663742120465708</v>
+        <v>0.3624042357053101</v>
       </c>
       <c r="O13">
-        <v>0.34449497645607019</v>
+        <v>0.3472011425747891</v>
       </c>
       <c r="P13">
-        <v>0.32512676685810438</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.3335695501644641</v>
+      </c>
+      <c r="Q13">
+        <v>0.3098875888149819</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>0.2497233182385899</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.35968307540112171</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C14">
+        <v>0.2511451594787084</v>
       </c>
       <c r="D14">
-        <v>0.41555389083238492</v>
+        <v>0.3599860842286571</v>
       </c>
       <c r="E14">
-        <v>0.44776978434917908</v>
+        <v>0.4134914925287242</v>
       </c>
       <c r="F14">
-        <v>0.46098097018210871</v>
+        <v>0.449548933898287</v>
       </c>
       <c r="G14">
-        <v>0.48836766249642521</v>
+        <v>0.4622666269656813</v>
       </c>
       <c r="H14">
-        <v>0.46882311218628903</v>
+        <v>0.4849545854439145</v>
       </c>
       <c r="I14">
-        <v>0.48648689757380581</v>
+        <v>0.4669157471151033</v>
       </c>
       <c r="J14">
-        <v>0.48752914163399541</v>
+        <v>0.4836203943142683</v>
       </c>
       <c r="K14">
-        <v>0.48976430344845129</v>
+        <v>0.4863889001113031</v>
       </c>
       <c r="L14">
-        <v>0.46698880715238522</v>
+        <v>0.483418162170459</v>
       </c>
       <c r="M14">
-        <v>0.43437087234532817</v>
+        <v>0.4633685793505296</v>
       </c>
       <c r="N14">
-        <v>0.45592572090150729</v>
+        <v>0.4307381889220291</v>
       </c>
       <c r="O14">
-        <v>0.48918778128960011</v>
+        <v>0.4522299929967523</v>
       </c>
       <c r="P14">
-        <v>0.5169593738848931</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.4802154965186037</v>
+      </c>
+      <c r="Q14">
+        <v>0.5041328082090845</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.24458666238129431</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0.35504457012995999</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C15">
+        <v>0.2507258044486836</v>
       </c>
       <c r="D15">
-        <v>0.40732729781329191</v>
+        <v>0.3625542854880255</v>
       </c>
       <c r="E15">
-        <v>0.44262163127304421</v>
+        <v>0.4223311262091046</v>
       </c>
       <c r="F15">
-        <v>0.45385969252357661</v>
+        <v>0.4535467812821318</v>
       </c>
       <c r="G15">
-        <v>0.47958677753349632</v>
+        <v>0.4667058662625584</v>
       </c>
       <c r="H15">
-        <v>0.4529901257774514</v>
+        <v>0.4950729027362859</v>
       </c>
       <c r="I15">
-        <v>0.47650788028605462</v>
+        <v>0.4712141464293844</v>
       </c>
       <c r="J15">
-        <v>0.47961669851424948</v>
+        <v>0.4881033684246552</v>
       </c>
       <c r="K15">
-        <v>0.47783774384601141</v>
+        <v>0.4905369733522658</v>
       </c>
       <c r="L15">
-        <v>0.45671968656671758</v>
+        <v>0.4901093868785527</v>
       </c>
       <c r="M15">
-        <v>0.41960237073461842</v>
+        <v>0.469504086949911</v>
       </c>
       <c r="N15">
-        <v>0.44473036064154953</v>
+        <v>0.4366705230230624</v>
       </c>
       <c r="O15">
-        <v>0.46884475330171149</v>
+        <v>0.4635008876702033</v>
       </c>
       <c r="P15">
-        <v>0.49749119639339939</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.4932969981518822</v>
+      </c>
+      <c r="Q15">
+        <v>0.5143450701496658</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.2477303371550926</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0.35588945867578542</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C16">
+        <v>0.2492377059458031</v>
       </c>
       <c r="D16">
-        <v>0.41287751111218418</v>
+        <v>0.3562692361829289</v>
       </c>
       <c r="E16">
-        <v>0.44812019618050147</v>
+        <v>0.4085783965302867</v>
       </c>
       <c r="F16">
-        <v>0.46008128028202261</v>
+        <v>0.4434554614849002</v>
       </c>
       <c r="G16">
-        <v>0.48596661711998529</v>
+        <v>0.4498238301935003</v>
       </c>
       <c r="H16">
-        <v>0.46448840617249593</v>
+        <v>0.480830616981963</v>
       </c>
       <c r="I16">
-        <v>0.4827706822783473</v>
+        <v>0.4581018490977216</v>
       </c>
       <c r="J16">
-        <v>0.48316273559314371</v>
+        <v>0.4790961001108217</v>
       </c>
       <c r="K16">
-        <v>0.48263460109655221</v>
+        <v>0.4826804147068232</v>
       </c>
       <c r="L16">
-        <v>0.46563056704204708</v>
+        <v>0.4827582873675472</v>
       </c>
       <c r="M16">
-        <v>0.42860174522250349</v>
+        <v>0.4706227777703694</v>
       </c>
       <c r="N16">
-        <v>0.45135216222488311</v>
+        <v>0.4462471038386548</v>
       </c>
       <c r="O16">
-        <v>0.48152828590457941</v>
+        <v>0.4702769471654465</v>
       </c>
       <c r="P16">
-        <v>0.50335438524722942</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.4954880815959462</v>
+      </c>
+      <c r="Q16">
+        <v>0.521116968583603</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.2495260357015264</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0.35814200583286038</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C17">
+        <v>0.2497783177529485</v>
       </c>
       <c r="D17">
-        <v>0.41285385452949719</v>
+        <v>0.3570661560792529</v>
       </c>
       <c r="E17">
-        <v>0.44695529179041621</v>
+        <v>0.4138689221780159</v>
       </c>
       <c r="F17">
-        <v>0.45848941532021092</v>
+        <v>0.4477628665565128</v>
       </c>
       <c r="G17">
-        <v>0.4821236622718158</v>
+        <v>0.4602671098740094</v>
       </c>
       <c r="H17">
-        <v>0.46021333986661711</v>
+        <v>0.4857704474261018</v>
       </c>
       <c r="I17">
-        <v>0.4791204977016531</v>
+        <v>0.4626450523579944</v>
       </c>
       <c r="J17">
-        <v>0.47994374508380239</v>
+        <v>0.4846821260246589</v>
       </c>
       <c r="K17">
-        <v>0.47962350917066943</v>
+        <v>0.4875397063622021</v>
       </c>
       <c r="L17">
-        <v>0.45665664964935088</v>
+        <v>0.4889400214071395</v>
       </c>
       <c r="M17">
-        <v>0.42672374675626279</v>
+        <v>0.4689869579359814</v>
       </c>
       <c r="N17">
-        <v>0.44860826806263587</v>
+        <v>0.44165802887296</v>
       </c>
       <c r="O17">
-        <v>0.47757381711234032</v>
+        <v>0.4648673923682353</v>
       </c>
       <c r="P17">
-        <v>0.50116920326476722</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="2">
-        <v>0.38373486156678371</v>
+        <v>0.494260237618079</v>
+      </c>
+      <c r="Q17">
+        <v>0.5142388706214993</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>-0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.38462301801476578</v>
+        <v>0.3833645114847191</v>
       </c>
       <c r="D18">
-        <v>0.38027805464217851</v>
+        <v>0.387728260697601</v>
       </c>
       <c r="E18">
-        <v>0.34378182633721838</v>
+        <v>0.384812623908582</v>
       </c>
       <c r="F18">
-        <v>0.37275797102886582</v>
+        <v>0.3497336401069608</v>
       </c>
       <c r="G18">
-        <v>0.34572857779208821</v>
+        <v>0.3728893346227981</v>
       </c>
       <c r="H18">
-        <v>0.39663713100858911</v>
+        <v>0.3479466363811356</v>
       </c>
       <c r="I18">
-        <v>0.44527223376025837</v>
+        <v>0.4008997915988287</v>
       </c>
       <c r="J18">
-        <v>0.4745601947321928</v>
+        <v>0.4519345665205281</v>
       </c>
       <c r="K18">
-        <v>0.48910254486086291</v>
+        <v>0.4829099468792745</v>
       </c>
       <c r="L18">
-        <v>0.48176791819911241</v>
+        <v>0.4959306031621137</v>
       </c>
       <c r="M18">
-        <v>0.48127448606235212</v>
+        <v>0.4938567906390329</v>
       </c>
       <c r="N18">
-        <v>0.45973914006765793</v>
+        <v>0.4913220316646303</v>
       </c>
       <c r="O18">
-        <v>0.45232631712331772</v>
+        <v>0.4701656986578706</v>
       </c>
       <c r="P18">
-        <v>0.44858265166198541</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="2">
-        <v>0.38335311966087771</v>
+        <v>0.4621590667450476</v>
+      </c>
+      <c r="Q18">
+        <v>0.455056834507368</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.3938189935590658</v>
+        <v>0.3835219442377737</v>
       </c>
       <c r="D19">
-        <v>0.39658363462535268</v>
+        <v>0.3933698403387545</v>
       </c>
       <c r="E19">
-        <v>0.29967221182624898</v>
+        <v>0.3956537763960905</v>
       </c>
       <c r="F19">
-        <v>0.34879866464518577</v>
+        <v>0.3039850470069296</v>
       </c>
       <c r="G19">
-        <v>0.37130651959800809</v>
+        <v>0.3496329797924843</v>
       </c>
       <c r="H19">
-        <v>0.45412419176090818</v>
+        <v>0.3762456646525595</v>
       </c>
       <c r="I19">
-        <v>0.45998001620194151</v>
+        <v>0.4593095930492814</v>
       </c>
       <c r="J19">
-        <v>0.50007787946014892</v>
+        <v>0.4600224189820891</v>
       </c>
       <c r="K19">
-        <v>0.5061844618969672</v>
+        <v>0.4983599550911427</v>
       </c>
       <c r="L19">
-        <v>0.48568993935431731</v>
+        <v>0.5044241041654975</v>
       </c>
       <c r="M19">
-        <v>0.47945983937772652</v>
+        <v>0.4822839905125683</v>
       </c>
       <c r="N19">
-        <v>0.48548749439723848</v>
+        <v>0.4729608045557541</v>
       </c>
       <c r="O19">
-        <v>0.48156150518387753</v>
+        <v>0.4779558990586422</v>
       </c>
       <c r="P19">
-        <v>0.49689998246942241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="2">
-        <v>0.3802690801944737</v>
+        <v>0.4792863454862909</v>
+      </c>
+      <c r="Q19">
+        <v>0.4893125312305567</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.38946175240662417</v>
+        <v>0.381097891968475</v>
       </c>
       <c r="D20">
-        <v>0.39012910321864658</v>
+        <v>0.3914217808587138</v>
       </c>
       <c r="E20">
-        <v>0.36809486660150281</v>
+        <v>0.39524575252739</v>
       </c>
       <c r="F20">
-        <v>0.34684873220119328</v>
+        <v>0.3753835241176309</v>
       </c>
       <c r="G20">
-        <v>0.36842934334863969</v>
+        <v>0.3572865554013317</v>
       </c>
       <c r="H20">
-        <v>0.43711763145435589</v>
+        <v>0.3819289953111136</v>
       </c>
       <c r="I20">
-        <v>0.48805520488673798</v>
+        <v>0.4415829308696476</v>
       </c>
       <c r="J20">
-        <v>0.51469650902848296</v>
+        <v>0.4966993563379444</v>
       </c>
       <c r="K20">
-        <v>0.49362431466490703</v>
+        <v>0.5195501200676054</v>
       </c>
       <c r="L20">
-        <v>0.47634812889056161</v>
+        <v>0.497969052600726</v>
       </c>
       <c r="M20">
-        <v>0.46258375780261451</v>
+        <v>0.4899849593242039</v>
       </c>
       <c r="N20">
-        <v>0.46073067508659088</v>
+        <v>0.4753763124544733</v>
       </c>
       <c r="O20">
-        <v>0.48922138632268991</v>
+        <v>0.473447545676061</v>
       </c>
       <c r="P20">
-        <v>0.4953842694316653</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.4973786561521553</v>
+      </c>
+      <c r="Q20">
+        <v>0.5067214666582461</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.29332305815037291</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>0.38409662544220119</v>
+        <v>0.2883917063056697</v>
       </c>
       <c r="D21">
-        <v>0.40091208529526617</v>
+        <v>0.3802515650175102</v>
       </c>
       <c r="E21">
-        <v>0.41185455037350682</v>
+        <v>0.39627126899958</v>
       </c>
       <c r="F21">
-        <v>0.38277279774314749</v>
+        <v>0.4059854541337977</v>
       </c>
       <c r="G21">
-        <v>0.40343525143556491</v>
+        <v>0.3774921140541503</v>
       </c>
       <c r="H21">
-        <v>0.3658249087938783</v>
+        <v>0.3965360492319528</v>
       </c>
       <c r="I21">
-        <v>0.37182965120172301</v>
+        <v>0.3664231823479155</v>
       </c>
       <c r="J21">
-        <v>0.37499066223125699</v>
+        <v>0.3729869794990391</v>
       </c>
       <c r="K21">
-        <v>0.34852438225478072</v>
+        <v>0.3742085430326301</v>
       </c>
       <c r="L21">
-        <v>0.30712230415953717</v>
+        <v>0.3542261367941117</v>
       </c>
       <c r="M21">
-        <v>0.285937871701195</v>
+        <v>0.3141438471246202</v>
       </c>
       <c r="N21">
-        <v>0.2306889402046437</v>
+        <v>0.3013425295471283</v>
       </c>
       <c r="O21">
-        <v>0.19361301516336241</v>
+        <v>0.2444195256770914</v>
       </c>
       <c r="P21">
-        <v>0.17707550971906891</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.2113006245358389</v>
+      </c>
+      <c r="Q21">
+        <v>0.1867797359178118</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.29312974070869119</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>0.38512965171687891</v>
+        <v>0.2927807242767062</v>
       </c>
       <c r="D22">
-        <v>0.40087419664445112</v>
+        <v>0.3829420664421546</v>
       </c>
       <c r="E22">
-        <v>0.40900844421800331</v>
+        <v>0.3986420379659822</v>
       </c>
       <c r="F22">
-        <v>0.38204344400492679</v>
+        <v>0.4074239475876272</v>
       </c>
       <c r="G22">
-        <v>0.4022388186326345</v>
+        <v>0.3803246038290098</v>
       </c>
       <c r="H22">
-        <v>0.35206414542810488</v>
+        <v>0.4033712356891015</v>
       </c>
       <c r="I22">
-        <v>0.34445393516943101</v>
+        <v>0.3521505438862435</v>
       </c>
       <c r="J22">
-        <v>0.35362680193294871</v>
+        <v>0.3398486264684529</v>
       </c>
       <c r="K22">
-        <v>0.33249362687504952</v>
+        <v>0.346999419368809</v>
       </c>
       <c r="L22">
-        <v>0.29734800300000491</v>
+        <v>0.3252221374719392</v>
       </c>
       <c r="M22">
-        <v>0.28530897472072542</v>
+        <v>0.2908824199872014</v>
       </c>
       <c r="N22">
-        <v>0.25063242444980971</v>
+        <v>0.2806331507651737</v>
       </c>
       <c r="O22">
-        <v>0.20300320312280071</v>
+        <v>0.2380884130662845</v>
       </c>
       <c r="P22">
-        <v>0.1918192438599928</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.1939235156741459</v>
+      </c>
+      <c r="Q22">
+        <v>0.1845028264009044</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>0.38385460037954561</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>0.29784388260831057</v>
+        <v>0.384314994411741</v>
       </c>
       <c r="D23">
-        <v>0.34132289720987052</v>
+        <v>0.3001631091521257</v>
       </c>
       <c r="E23">
-        <v>0.38450868688839751</v>
+        <v>0.3494683322558808</v>
       </c>
       <c r="F23">
-        <v>0.38647684031817531</v>
+        <v>0.397903869243511</v>
       </c>
       <c r="G23">
-        <v>0.40173113245711911</v>
+        <v>0.3946077375052453</v>
       </c>
       <c r="H23">
-        <v>0.37862388131725161</v>
+        <v>0.4054618345500302</v>
       </c>
       <c r="I23">
-        <v>0.36723094412180068</v>
+        <v>0.3783418153833716</v>
       </c>
       <c r="J23">
-        <v>0.32986590013112821</v>
+        <v>0.3671090490720525</v>
       </c>
       <c r="K23">
-        <v>0.30834712029215799</v>
+        <v>0.3325462409952198</v>
       </c>
       <c r="L23">
-        <v>0.28204395880469951</v>
+        <v>0.3207135435916073</v>
       </c>
       <c r="M23">
-        <v>0.28663155310299349</v>
+        <v>0.2938668784441631</v>
       </c>
       <c r="N23">
-        <v>0.28176863299534338</v>
+        <v>0.2964184892746515</v>
       </c>
       <c r="O23">
-        <v>0.27103977559068182</v>
+        <v>0.2876078718184767</v>
       </c>
       <c r="P23">
-        <v>0.24495640353389689</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.2709700235834649</v>
+      </c>
+      <c r="Q23">
+        <v>0.2384354894896848</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>1.145249591600791E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>-0.1231772731881617</v>
+        <v>0.3696960827240271</v>
       </c>
       <c r="D24">
-        <v>-0.13881686592372219</v>
+        <v>0.4090259324712235</v>
       </c>
       <c r="E24">
-        <v>-0.1848223997237729</v>
+        <v>0.4327761578158785</v>
       </c>
       <c r="F24">
-        <v>-0.34586556077331337</v>
+        <v>0.4564505914872983</v>
       </c>
       <c r="G24">
-        <v>-0.34296413750221738</v>
+        <v>0.416040740160247</v>
       </c>
       <c r="H24">
-        <v>-0.33148502201187291</v>
+        <v>0.3813080475083899</v>
       </c>
       <c r="I24">
-        <v>-0.38413585775515591</v>
+        <v>0.3519928778189446</v>
       </c>
       <c r="J24">
-        <v>-0.4508393108160636</v>
+        <v>0.4487898233039224</v>
       </c>
       <c r="K24">
-        <v>-0.60014231121493911</v>
+        <v>0.488714255317068</v>
       </c>
       <c r="L24">
-        <v>-0.59095295660357572</v>
+        <v>0.4691516745755496</v>
       </c>
       <c r="M24">
-        <v>-0.54518267027280343</v>
+        <v>0.4969920988457758</v>
       </c>
       <c r="N24">
-        <v>-0.49153397560795947</v>
+        <v>0.455418652507026</v>
       </c>
       <c r="O24">
-        <v>-0.44986287799899932</v>
+        <v>0.4527509530085409</v>
       </c>
       <c r="P24">
-        <v>-0.43605079507461619</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.4317578897365256</v>
+      </c>
+      <c r="Q24">
+        <v>0.3997449486212359</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-4.2156463013841997E-3</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>-0.11895412189300229</v>
+        <v>0.3695585709384494</v>
       </c>
       <c r="D25">
-        <v>-0.16838918486031729</v>
+        <v>0.4128819991991191</v>
       </c>
       <c r="E25">
-        <v>-0.33311900795502741</v>
+        <v>0.4398699005959987</v>
       </c>
       <c r="F25">
-        <v>-0.34307439724185262</v>
+        <v>0.4640725760355521</v>
       </c>
       <c r="G25">
-        <v>-0.44755876769859793</v>
+        <v>0.4095812523453043</v>
       </c>
       <c r="H25">
-        <v>-0.65077597588349567</v>
+        <v>0.4184483657649811</v>
       </c>
       <c r="I25">
-        <v>-0.74971973257113877</v>
+        <v>0.4048638322543136</v>
       </c>
       <c r="J25">
-        <v>-0.68848934033894482</v>
+        <v>0.4626018744813217</v>
       </c>
       <c r="K25">
-        <v>-0.72695542150444636</v>
+        <v>0.5082570861540041</v>
       </c>
       <c r="L25">
-        <v>-0.7875040065329677</v>
+        <v>0.5171248529513998</v>
       </c>
       <c r="M25">
-        <v>-0.88789330359486429</v>
+        <v>0.5330419977018518</v>
       </c>
       <c r="N25">
-        <v>-0.97059950806978734</v>
+        <v>0.5441062103569918</v>
       </c>
       <c r="O25">
-        <v>-0.93182686323477193</v>
+        <v>0.5280982345229061</v>
       </c>
       <c r="P25">
-        <v>-0.91974767988889061</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.5117376468617409</v>
+      </c>
+      <c r="Q25">
+        <v>0.4804558902687341</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>1.3499371161112699E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>-4.3227899516354577E-2</v>
+        <v>0.3822288614849516</v>
       </c>
       <c r="D26">
-        <v>-4.8983857734805132E-2</v>
+        <v>0.4041062581582097</v>
       </c>
       <c r="E26">
-        <v>-0.15790497228934011</v>
+        <v>0.4165469434330892</v>
       </c>
       <c r="F26">
-        <v>-0.21466833542978259</v>
+        <v>0.4367833340889968</v>
       </c>
       <c r="G26">
-        <v>-0.16430472445202909</v>
+        <v>0.3919767434649949</v>
       </c>
       <c r="H26">
-        <v>-0.12380937750226161</v>
+        <v>0.3809086169983364</v>
       </c>
       <c r="I26">
-        <v>-0.14194548495656251</v>
+        <v>0.3823885975885008</v>
       </c>
       <c r="J26">
-        <v>-0.14120074186041839</v>
+        <v>0.45794798000607</v>
       </c>
       <c r="K26">
-        <v>-6.8592686971046535E-2</v>
+        <v>0.5123446478855702</v>
       </c>
       <c r="L26">
-        <v>-0.24945480383465299</v>
+        <v>0.4863478085820813</v>
       </c>
       <c r="M26">
-        <v>-0.3438511963575826</v>
+        <v>0.5059739380322417</v>
       </c>
       <c r="N26">
-        <v>-0.32965400250926269</v>
+        <v>0.5102414875807402</v>
       </c>
       <c r="O26">
-        <v>-0.38542210265372912</v>
+        <v>0.5033958977420239</v>
       </c>
       <c r="P26">
-        <v>-0.41328056450334882</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.481594318739881</v>
+      </c>
+      <c r="Q26">
+        <v>0.4381683526238094</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>1.3359144263879189E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>-1.340377944453354E-2</v>
+        <v>0.382008518637945</v>
       </c>
       <c r="D27">
-        <v>-0.25736203672223451</v>
+        <v>0.4060561758288374</v>
       </c>
       <c r="E27">
-        <v>-0.1913604865401671</v>
+        <v>0.4211336129182429</v>
       </c>
       <c r="F27">
-        <v>-0.1171785880590388</v>
+        <v>0.4396327073757894</v>
       </c>
       <c r="G27">
-        <v>-0.1322758681461752</v>
+        <v>0.4044009995157333</v>
       </c>
       <c r="H27">
-        <v>-0.1273916677934635</v>
+        <v>0.3923437990845637</v>
       </c>
       <c r="I27">
-        <v>-6.9549870758506452E-2</v>
+        <v>0.3837337475561144</v>
       </c>
       <c r="J27">
-        <v>-0.1567287588909389</v>
+        <v>0.441085134416708</v>
       </c>
       <c r="K27">
-        <v>-0.2358700408440132</v>
+        <v>0.5000066599269241</v>
       </c>
       <c r="L27">
-        <v>-0.28444571292787968</v>
+        <v>0.4988872632309372</v>
       </c>
       <c r="M27">
-        <v>-0.3339756142932086</v>
+        <v>0.51733235924589</v>
       </c>
       <c r="N27">
-        <v>-0.33327305331691731</v>
+        <v>0.5362677910844659</v>
       </c>
       <c r="O27">
-        <v>-0.41852968588180839</v>
+        <v>0.5569275108212388</v>
       </c>
       <c r="P27">
-        <v>-0.48109689058405342</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.5355453854312048</v>
+      </c>
+      <c r="Q27">
+        <v>0.5578526356662764</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.37045965903778511</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.41131530211772671</v>
+        <v>0.3695407790975224</v>
       </c>
       <c r="D28">
-        <v>0.43583280400466529</v>
+        <v>0.4118832350899493</v>
       </c>
       <c r="E28">
-        <v>0.45868753894111092</v>
+        <v>0.4381582778790712</v>
       </c>
       <c r="F28">
-        <v>0.41924447537992221</v>
+        <v>0.4632175708047901</v>
       </c>
       <c r="G28">
-        <v>0.38197767548190381</v>
+        <v>0.4128500700854689</v>
       </c>
       <c r="H28">
-        <v>0.34845198116105908</v>
+        <v>0.4144185348471239</v>
       </c>
       <c r="I28">
-        <v>0.44124889254067051</v>
+        <v>0.4020666231951129</v>
       </c>
       <c r="J28">
-        <v>0.48766532623335118</v>
+        <v>0.4476758728468672</v>
       </c>
       <c r="K28">
-        <v>0.46925222901319308</v>
+        <v>0.4897127569205746</v>
       </c>
       <c r="L28">
-        <v>0.49685776164297979</v>
+        <v>0.525885217198227</v>
       </c>
       <c r="M28">
-        <v>0.45386362658286811</v>
+        <v>0.5412449815975273</v>
       </c>
       <c r="N28">
-        <v>0.45109316498183882</v>
+        <v>0.5593748447250418</v>
       </c>
       <c r="O28">
-        <v>0.43059987752313739</v>
+        <v>0.5431222628530148</v>
       </c>
       <c r="P28">
-        <v>0.40081366630514381</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.5520545506102055</v>
+      </c>
+      <c r="Q28">
+        <v>0.5356925383687496</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.36859859897067832</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.40959240565631427</v>
+        <v>0.3670604435139561</v>
       </c>
       <c r="D29">
-        <v>0.43706192940361899</v>
+        <v>0.4068313773225309</v>
       </c>
       <c r="E29">
-        <v>0.46325484023511238</v>
+        <v>0.4334549210778858</v>
       </c>
       <c r="F29">
-        <v>0.40398152819659389</v>
+        <v>0.4599052602904242</v>
       </c>
       <c r="G29">
-        <v>0.40878020132588933</v>
+        <v>0.4090691864843249</v>
       </c>
       <c r="H29">
-        <v>0.39868093292388668</v>
+        <v>0.4143094864262006</v>
       </c>
       <c r="I29">
-        <v>0.45940743631644521</v>
+        <v>0.3991270356948542</v>
       </c>
       <c r="J29">
-        <v>0.50402235350015379</v>
+        <v>0.4418717253433216</v>
       </c>
       <c r="K29">
-        <v>0.51712172783789889</v>
+        <v>0.4823092348444888</v>
       </c>
       <c r="L29">
-        <v>0.53073846451905582</v>
+        <v>0.5209959934618322</v>
       </c>
       <c r="M29">
-        <v>0.53805717731684399</v>
+        <v>0.5438263408465523</v>
       </c>
       <c r="N29">
-        <v>0.52415740106340591</v>
+        <v>0.5615974232295859</v>
       </c>
       <c r="O29">
-        <v>0.50417516895077941</v>
+        <v>0.5451587554684784</v>
       </c>
       <c r="P29">
-        <v>0.47474726314848481</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.5512466125097173</v>
+      </c>
+      <c r="Q29">
+        <v>0.5307810111297213</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.38095702087491162</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.40384411974891499</v>
+        <v>0.3700343704202532</v>
       </c>
       <c r="D30">
-        <v>0.41605619836810431</v>
+        <v>0.4124442069639135</v>
       </c>
       <c r="E30">
-        <v>0.4352329517588458</v>
+        <v>0.4391846999655908</v>
       </c>
       <c r="F30">
-        <v>0.39289966557688411</v>
+        <v>0.4651678800409982</v>
       </c>
       <c r="G30">
-        <v>0.37981493220787099</v>
+        <v>0.4117149029046683</v>
       </c>
       <c r="H30">
-        <v>0.37930113504857033</v>
+        <v>0.4151286083055208</v>
       </c>
       <c r="I30">
-        <v>0.45489463789359941</v>
+        <v>0.4048771622757086</v>
       </c>
       <c r="J30">
-        <v>0.50789824386339655</v>
+        <v>0.4429697458826409</v>
       </c>
       <c r="K30">
-        <v>0.48204436706357628</v>
+        <v>0.4873778196967786</v>
       </c>
       <c r="L30">
-        <v>0.50278390506291493</v>
+        <v>0.5131458595439531</v>
       </c>
       <c r="M30">
-        <v>0.50605393875022797</v>
+        <v>0.5409523870824485</v>
       </c>
       <c r="N30">
-        <v>0.49979809749506188</v>
+        <v>0.5582160705094229</v>
       </c>
       <c r="O30">
-        <v>0.47210892780685432</v>
+        <v>0.5376637193364752</v>
       </c>
       <c r="P30">
-        <v>0.42761105017450612</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.5454775377983291</v>
+      </c>
+      <c r="Q30">
+        <v>0.5242792985619303</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.38288864856871552</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.40481973289056727</v>
+        <v>0.3701557180928794</v>
       </c>
       <c r="D31">
-        <v>0.41336024029010549</v>
+        <v>0.4128905883599487</v>
       </c>
       <c r="E31">
-        <v>0.44065904428130448</v>
+        <v>0.4421156219704221</v>
       </c>
       <c r="F31">
-        <v>0.39660164645292428</v>
+        <v>0.4673377967245754</v>
       </c>
       <c r="G31">
-        <v>0.38164407165349512</v>
+        <v>0.4208008777817481</v>
       </c>
       <c r="H31">
-        <v>0.37355260751527247</v>
+        <v>0.4187893098566876</v>
       </c>
       <c r="I31">
-        <v>0.44132269978455713</v>
+        <v>0.4061917500471381</v>
       </c>
       <c r="J31">
-        <v>0.50245410004861291</v>
+        <v>0.4428303318326319</v>
       </c>
       <c r="K31">
-        <v>0.49812094739078872</v>
+        <v>0.487722425955446</v>
       </c>
       <c r="L31">
-        <v>0.51424534647636377</v>
+        <v>0.5157806539930859</v>
       </c>
       <c r="M31">
-        <v>0.52902551887758276</v>
+        <v>0.543436653696753</v>
       </c>
       <c r="N31">
-        <v>0.55720047224203872</v>
+        <v>0.5621266518658637</v>
       </c>
       <c r="O31">
-        <v>0.53574538068271749</v>
+        <v>0.5461117753001672</v>
       </c>
       <c r="P31">
-        <v>0.55885066136020856</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.5567040641398991</v>
+      </c>
+      <c r="Q31">
+        <v>0.5399128016236359</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.36982669924919659</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.41051708056888081</v>
+        <v>0.3698425571400623</v>
       </c>
       <c r="D32">
-        <v>0.4359520477805004</v>
+        <v>0.4126990873584379</v>
       </c>
       <c r="E32">
-        <v>0.46219483840832482</v>
+        <v>0.4404188398641343</v>
       </c>
       <c r="F32">
-        <v>0.41233346784647318</v>
+        <v>0.4656655712405726</v>
       </c>
       <c r="G32">
-        <v>0.4157574002451323</v>
+        <v>0.4130861042240462</v>
       </c>
       <c r="H32">
-        <v>0.40131616249506241</v>
+        <v>0.4162089170321374</v>
       </c>
       <c r="I32">
-        <v>0.4403859413066748</v>
+        <v>0.3967133310941121</v>
       </c>
       <c r="J32">
-        <v>0.48157158079577839</v>
+        <v>0.4471989772176665</v>
       </c>
       <c r="K32">
-        <v>0.51618907119119728</v>
+        <v>0.4813973836829292</v>
       </c>
       <c r="L32">
-        <v>0.53556080591058364</v>
+        <v>0.5090824642925623</v>
       </c>
       <c r="M32">
-        <v>0.55523602238077008</v>
+        <v>0.5265908872800473</v>
       </c>
       <c r="N32">
-        <v>0.54019267502757184</v>
+        <v>0.5440425395561027</v>
       </c>
       <c r="O32">
-        <v>0.54862736276309865</v>
+        <v>0.5271635934705152</v>
       </c>
       <c r="P32">
-        <v>0.52853131523722363</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.5354984826657722</v>
+      </c>
+      <c r="Q32">
+        <v>0.5097829642669133</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.36820785851934779</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.40922568397562092</v>
+        <v>0.365236212327393</v>
       </c>
       <c r="D33">
-        <v>0.43608517856836132</v>
+        <v>0.4064138210196177</v>
       </c>
       <c r="E33">
-        <v>0.4629322214229426</v>
+        <v>0.4362250575815465</v>
       </c>
       <c r="F33">
-        <v>0.41382713051746589</v>
+        <v>0.4609961400474422</v>
       </c>
       <c r="G33">
-        <v>0.41835526394652373</v>
+        <v>0.4065623841605839</v>
       </c>
       <c r="H33">
-        <v>0.40596622874554211</v>
+        <v>0.4074151548145499</v>
       </c>
       <c r="I33">
-        <v>0.44756344516192431</v>
+        <v>0.3998932692708541</v>
       </c>
       <c r="J33">
-        <v>0.48469969545075542</v>
+        <v>0.4506676602686132</v>
       </c>
       <c r="K33">
-        <v>0.52089581641408778</v>
+        <v>0.4850502243166742</v>
       </c>
       <c r="L33">
-        <v>0.54476421320998736</v>
+        <v>0.5169675400395088</v>
       </c>
       <c r="M33">
-        <v>0.56397410354323241</v>
+        <v>0.5379098798160777</v>
       </c>
       <c r="N33">
-        <v>0.54509067441071735</v>
+        <v>0.5541553647246285</v>
       </c>
       <c r="O33">
-        <v>0.55477945741966894</v>
+        <v>0.5434644105833086</v>
       </c>
       <c r="P33">
-        <v>0.53041519026670481</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.5466660366010209</v>
+      </c>
+      <c r="Q33">
+        <v>0.5214522457754576</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.37230553964152918</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.41411793710603662</v>
+        <v>0.3673370298067099</v>
       </c>
       <c r="D34">
-        <v>0.44186341744046481</v>
+        <v>0.4105547786805705</v>
       </c>
       <c r="E34">
-        <v>0.46551268443113297</v>
+        <v>0.436066404387325</v>
       </c>
       <c r="F34">
-        <v>0.41255173431993042</v>
+        <v>0.4618926141536854</v>
       </c>
       <c r="G34">
-        <v>0.41698351332555539</v>
+        <v>0.4160801592405972</v>
       </c>
       <c r="H34">
-        <v>0.40301509434762389</v>
+        <v>0.4205602373862453</v>
       </c>
       <c r="I34">
-        <v>0.44357294436112649</v>
+        <v>0.4114927055184366</v>
       </c>
       <c r="J34">
-        <v>0.48705490460349082</v>
+        <v>0.4490807729455636</v>
       </c>
       <c r="K34">
-        <v>0.520019973826924</v>
+        <v>0.4850137162013524</v>
       </c>
       <c r="L34">
-        <v>0.54310397591463533</v>
+        <v>0.511510918030302</v>
       </c>
       <c r="M34">
-        <v>0.56238922815297843</v>
+        <v>0.5306586725182011</v>
       </c>
       <c r="N34">
-        <v>0.54660942761353482</v>
+        <v>0.5493364370041018</v>
       </c>
       <c r="O34">
-        <v>0.55253501028182983</v>
+        <v>0.5351348705138209</v>
       </c>
       <c r="P34">
-        <v>0.53329613494562322</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.543017474903826</v>
+      </c>
+      <c r="Q34">
+        <v>0.5094649451152956</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.36632229190693461</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.40809650956113191</v>
+        <v>0.3680870342294672</v>
       </c>
       <c r="D35">
-        <v>0.43353215448548932</v>
+        <v>0.4102809676452555</v>
       </c>
       <c r="E35">
-        <v>0.46037851845004829</v>
+        <v>0.4381437866302704</v>
       </c>
       <c r="F35">
-        <v>0.4079490765047753</v>
+        <v>0.4646955829049553</v>
       </c>
       <c r="G35">
-        <v>0.40520406432252032</v>
+        <v>0.4200564166194642</v>
       </c>
       <c r="H35">
-        <v>0.39215555212327258</v>
+        <v>0.4248997206491808</v>
       </c>
       <c r="I35">
-        <v>0.43503482090479101</v>
+        <v>0.4099752316765775</v>
       </c>
       <c r="J35">
-        <v>0.46996719079089011</v>
+        <v>0.450661683415164</v>
       </c>
       <c r="K35">
-        <v>0.50465244084073979</v>
+        <v>0.4918217917443326</v>
       </c>
       <c r="L35">
-        <v>0.53148032238610299</v>
+        <v>0.5103088867187048</v>
       </c>
       <c r="M35">
-        <v>0.55110362501044963</v>
+        <v>0.5397364060419207</v>
       </c>
       <c r="N35">
-        <v>0.53302101391217349</v>
+        <v>0.5581592180865024</v>
       </c>
       <c r="O35">
-        <v>0.54133763622742315</v>
+        <v>0.550688639719164</v>
       </c>
       <c r="P35">
-        <v>0.52094703123028263</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.5558581117720182</v>
+      </c>
+      <c r="Q35">
+        <v>0.5297612731372786</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.37172355871279761</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.41430340602558352</v>
+        <v>0.3690812076304958</v>
       </c>
       <c r="D36">
-        <v>0.44154044795119762</v>
+        <v>0.4127438120301646</v>
       </c>
       <c r="E36">
-        <v>0.46691900134990189</v>
+        <v>0.4408813457432804</v>
       </c>
       <c r="F36">
-        <v>0.4162815138715138</v>
+        <v>0.4669034989054155</v>
       </c>
       <c r="G36">
-        <v>0.42007854215468199</v>
+        <v>0.4196963156021561</v>
       </c>
       <c r="H36">
-        <v>0.40877178957875998</v>
+        <v>0.4241917603728708</v>
       </c>
       <c r="I36">
-        <v>0.45175109031098232</v>
+        <v>0.4101801237959334</v>
       </c>
       <c r="J36">
-        <v>0.48941985475572403</v>
+        <v>0.4453168420970782</v>
       </c>
       <c r="K36">
-        <v>0.51167372956567925</v>
+        <v>0.4891072637195936</v>
       </c>
       <c r="L36">
-        <v>0.53543885614060682</v>
+        <v>0.5144284060687081</v>
       </c>
       <c r="M36">
-        <v>0.54867953746478482</v>
+        <v>0.5420412520148636</v>
       </c>
       <c r="N36">
-        <v>0.53111783165550686</v>
+        <v>0.5597236659965487</v>
       </c>
       <c r="O36">
-        <v>0.54128510067952018</v>
+        <v>0.5478219717340516</v>
       </c>
       <c r="P36">
-        <v>0.51857757086070533</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.5556898970586867</v>
+      </c>
+      <c r="Q36">
+        <v>0.5293148113555859</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.36785093860868662</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>0.40639135644671781</v>
+        <v>0.3867884814767505</v>
       </c>
       <c r="D37">
-        <v>0.43125985077334622</v>
+        <v>0.4241213331238431</v>
       </c>
       <c r="E37">
-        <v>0.45926802877968093</v>
+        <v>0.48092554911756</v>
       </c>
       <c r="F37">
-        <v>0.40594276710181548</v>
+        <v>0.4637524845145033</v>
       </c>
       <c r="G37">
-        <v>0.41269718685917223</v>
+        <v>0.4137110548859394</v>
       </c>
       <c r="H37">
-        <v>0.3982886378636975</v>
+        <v>0.3355562826378947</v>
       </c>
       <c r="I37">
-        <v>0.44154139113220331</v>
+        <v>0.3759009337594185</v>
       </c>
       <c r="J37">
-        <v>0.47405045314718652</v>
+        <v>0.3808857014257404</v>
       </c>
       <c r="K37">
-        <v>0.50635431843994316</v>
+        <v>0.3901723308909197</v>
       </c>
       <c r="L37">
-        <v>0.52652178027713237</v>
+        <v>0.4137805953875301</v>
       </c>
       <c r="M37">
-        <v>0.54442712405845683</v>
+        <v>0.3785088846260483</v>
       </c>
       <c r="N37">
-        <v>0.53316357675040349</v>
+        <v>0.3666433713780484</v>
       </c>
       <c r="O37">
-        <v>0.54171300953423174</v>
+        <v>0.3535725560481373</v>
       </c>
       <c r="P37">
-        <v>0.51332675423492757</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.3478353855825749</v>
+      </c>
+      <c r="Q37">
+        <v>0.3359052277799937</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.36571291537063172</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>0.40959180408137619</v>
+        <v>0.388445091607253</v>
       </c>
       <c r="D38">
-        <v>0.43712702899841538</v>
+        <v>0.4288365015659965</v>
       </c>
       <c r="E38">
-        <v>0.4634820034345884</v>
+        <v>0.4757588581377876</v>
       </c>
       <c r="F38">
-        <v>0.41733851443208669</v>
+        <v>0.4500967620441435</v>
       </c>
       <c r="G38">
-        <v>0.42121374491983649</v>
+        <v>0.4055192048991963</v>
       </c>
       <c r="H38">
-        <v>0.40639946164424151</v>
+        <v>0.4377366140947089</v>
       </c>
       <c r="I38">
-        <v>0.45069713989807592</v>
+        <v>0.4674046875672881</v>
       </c>
       <c r="J38">
-        <v>0.49694244835453222</v>
+        <v>0.4749130509581651</v>
       </c>
       <c r="K38">
-        <v>0.51478453858644324</v>
+        <v>0.4783427962291093</v>
       </c>
       <c r="L38">
-        <v>0.53639681517574644</v>
+        <v>0.5099085245051993</v>
       </c>
       <c r="M38">
-        <v>0.55408552118041843</v>
+        <v>0.5051556839764776</v>
       </c>
       <c r="N38">
-        <v>0.54651894675823698</v>
+        <v>0.541362779538384</v>
       </c>
       <c r="O38">
-        <v>0.55441814650612298</v>
+        <v>0.5604117071804845</v>
       </c>
       <c r="P38">
-        <v>0.52698842637494192</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.5729924275625926</v>
+      </c>
+      <c r="Q38">
+        <v>0.5582576154789275</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.36973067468612608</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>0.41339382534258018</v>
+        <v>0.3896735879085711</v>
       </c>
       <c r="D39">
-        <v>0.43989535209827618</v>
+        <v>0.4370456062682597</v>
       </c>
       <c r="E39">
-        <v>0.46546743921637052</v>
+        <v>0.4794273396620081</v>
       </c>
       <c r="F39">
-        <v>0.42030361895662149</v>
+        <v>0.4571969734614078</v>
       </c>
       <c r="G39">
-        <v>0.42117345199563633</v>
+        <v>0.4142832953668043</v>
       </c>
       <c r="H39">
-        <v>0.4096078032678987</v>
+        <v>0.4601620181317899</v>
       </c>
       <c r="I39">
-        <v>0.45358569429262069</v>
+        <v>0.493406395287508</v>
       </c>
       <c r="J39">
-        <v>0.48901915481706187</v>
+        <v>0.4866940015820446</v>
       </c>
       <c r="K39">
-        <v>0.51401183508448722</v>
+        <v>0.5050989392175267</v>
       </c>
       <c r="L39">
-        <v>0.53603111923735614</v>
+        <v>0.5285408899797728</v>
       </c>
       <c r="M39">
-        <v>0.55623318430810254</v>
+        <v>0.5206615843327292</v>
       </c>
       <c r="N39">
-        <v>0.54601867697345474</v>
+        <v>0.5542601768116231</v>
       </c>
       <c r="O39">
-        <v>0.55347218626276828</v>
+        <v>0.5581114739064915</v>
       </c>
       <c r="P39">
-        <v>0.52539935993117926</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.5624691185331906</v>
+      </c>
+      <c r="Q39">
+        <v>0.5504447801851743</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.36855340971883471</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>0.41126861519882751</v>
+        <v>0.3676946234192229</v>
       </c>
       <c r="D40">
-        <v>0.44177769940429062</v>
+        <v>0.3758554087473784</v>
       </c>
       <c r="E40">
-        <v>0.46753197431913918</v>
+        <v>0.4369856735205176</v>
       </c>
       <c r="F40">
-        <v>0.41702670778833312</v>
+        <v>0.4478929110638538</v>
       </c>
       <c r="G40">
-        <v>0.41950818367321802</v>
+        <v>0.4466496764489786</v>
       </c>
       <c r="H40">
-        <v>0.41025590049972482</v>
+        <v>0.4774350472401884</v>
       </c>
       <c r="I40">
-        <v>0.44770758061626897</v>
+        <v>0.4724623315868685</v>
       </c>
       <c r="J40">
-        <v>0.48525284389336559</v>
+        <v>0.4691383787530197</v>
       </c>
       <c r="K40">
-        <v>0.50581502107881493</v>
+        <v>0.4545628610237212</v>
       </c>
       <c r="L40">
-        <v>0.53755086996181733</v>
+        <v>0.4366808904209428</v>
       </c>
       <c r="M40">
-        <v>0.5571412106467436</v>
+        <v>0.4474838629514395</v>
       </c>
       <c r="N40">
-        <v>0.54649604932199936</v>
+        <v>0.440270724030514</v>
       </c>
       <c r="O40">
-        <v>0.55830267275561452</v>
+        <v>0.4360047838096208</v>
       </c>
       <c r="P40">
-        <v>0.52811599253243091</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.4233062071340787</v>
+      </c>
+      <c r="Q40">
+        <v>0.3827079843214106</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.38780545281483769</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>0.42996170876584161</v>
+        <v>0.3691344883582927</v>
       </c>
       <c r="D41">
-        <v>0.48411981495518441</v>
+        <v>0.4050518255252602</v>
       </c>
       <c r="E41">
-        <v>0.46570021389045507</v>
+        <v>0.4069910421907419</v>
       </c>
       <c r="F41">
-        <v>0.40566658441795422</v>
+        <v>0.3811228528030958</v>
       </c>
       <c r="G41">
-        <v>0.3328000595160413</v>
+        <v>0.3565226904111241</v>
       </c>
       <c r="H41">
-        <v>0.36503634437005122</v>
+        <v>0.3287116858684616</v>
       </c>
       <c r="I41">
-        <v>0.37340735163466993</v>
+        <v>0.3196476389953499</v>
       </c>
       <c r="J41">
-        <v>0.38022543802443498</v>
+        <v>0.3148580656780419</v>
       </c>
       <c r="K41">
-        <v>0.40229110706056692</v>
+        <v>0.3041425104882377</v>
       </c>
       <c r="L41">
-        <v>0.36914632289270088</v>
+        <v>0.235033867937098</v>
       </c>
       <c r="M41">
-        <v>0.36028806390435991</v>
+        <v>0.2015413363381056</v>
       </c>
       <c r="N41">
-        <v>0.34859642436066052</v>
+        <v>0.1789118573553571</v>
       </c>
       <c r="O41">
-        <v>0.34416781035013061</v>
+        <v>0.1376659645252422</v>
       </c>
       <c r="P41">
-        <v>0.33068225213212948</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.1155472275858194</v>
+      </c>
+      <c r="Q41">
+        <v>0.1359632623841205</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.39013413744865127</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>0.42868431126181761</v>
+        <v>0.2823439445162646</v>
       </c>
       <c r="D42">
-        <v>0.47746941203292709</v>
+        <v>0.3828688133286583</v>
       </c>
       <c r="E42">
-        <v>0.44969005997803879</v>
+        <v>0.3836456570634245</v>
       </c>
       <c r="F42">
-        <v>0.40090704183284581</v>
+        <v>0.3503791010858415</v>
       </c>
       <c r="G42">
-        <v>0.43400984043551483</v>
+        <v>0.2969691585427706</v>
       </c>
       <c r="H42">
-        <v>0.46540943080396102</v>
+        <v>0.3122003830139767</v>
       </c>
       <c r="I42">
-        <v>0.47786786684531429</v>
+        <v>0.3386790521223579</v>
       </c>
       <c r="J42">
-        <v>0.47415443967791132</v>
+        <v>0.3248029677008727</v>
       </c>
       <c r="K42">
-        <v>0.50448559120681014</v>
+        <v>0.2506272534970736</v>
       </c>
       <c r="L42">
-        <v>0.50711872257774115</v>
+        <v>0.2198746343357302</v>
       </c>
       <c r="M42">
-        <v>0.5404778108302517</v>
+        <v>0.2059270731573702</v>
       </c>
       <c r="N42">
-        <v>0.56310715414468104</v>
+        <v>0.165083278886961</v>
       </c>
       <c r="O42">
-        <v>0.57633866042889637</v>
+        <v>0.1345954032972401</v>
       </c>
       <c r="P42">
-        <v>0.56067000840906056</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.1431350322412614</v>
+      </c>
+      <c r="Q42">
+        <v>0.157436537763063</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.39045721632695451</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>0.42639065803821441</v>
+        <v>0.3835001292552082</v>
       </c>
       <c r="D43">
-        <v>0.4788221396086435</v>
+        <v>0.3905681491915085</v>
       </c>
       <c r="E43">
-        <v>0.45128285230632492</v>
+        <v>0.3814256996874522</v>
       </c>
       <c r="F43">
-        <v>0.40536701410840692</v>
+        <v>0.3769385962713772</v>
       </c>
       <c r="G43">
-        <v>0.45055045995012521</v>
+        <v>0.3516560414640565</v>
       </c>
       <c r="H43">
-        <v>0.48809315732140979</v>
+        <v>0.3535598073616786</v>
       </c>
       <c r="I43">
-        <v>0.47753931879324119</v>
+        <v>0.3652097765844667</v>
       </c>
       <c r="J43">
-        <v>0.49485448809746901</v>
+        <v>0.3714957325142153</v>
       </c>
       <c r="K43">
-        <v>0.52422764467194216</v>
+        <v>0.3058305827424199</v>
       </c>
       <c r="L43">
-        <v>0.51650664298636828</v>
+        <v>0.3108190666998327</v>
       </c>
       <c r="M43">
-        <v>0.55643865763280698</v>
+        <v>0.298156004271416</v>
       </c>
       <c r="N43">
-        <v>0.56214211260455449</v>
+        <v>0.2810193204080305</v>
       </c>
       <c r="O43">
-        <v>0.57351923357560475</v>
+        <v>0.2861153047739614</v>
       </c>
       <c r="P43">
-        <v>0.56474339489053038</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>0.36898654942831721</v>
-      </c>
-      <c r="C44">
-        <v>0.37659693745130268</v>
-      </c>
-      <c r="D44">
-        <v>0.43979815257851262</v>
-      </c>
-      <c r="E44">
-        <v>0.44780904211092709</v>
-      </c>
-      <c r="F44">
-        <v>0.44589770956545621</v>
-      </c>
-      <c r="G44">
-        <v>0.47556187187550542</v>
-      </c>
-      <c r="H44">
-        <v>0.4704896776748953</v>
-      </c>
-      <c r="I44">
-        <v>0.46671716800146462</v>
-      </c>
-      <c r="J44">
-        <v>0.45672325211775522</v>
-      </c>
-      <c r="K44">
-        <v>0.4375567657442585</v>
-      </c>
-      <c r="L44">
-        <v>0.4493995260308406</v>
-      </c>
-      <c r="M44">
-        <v>0.44263720632796077</v>
-      </c>
-      <c r="N44">
-        <v>0.43881827378059862</v>
-      </c>
-      <c r="O44">
-        <v>0.42061530939657199</v>
-      </c>
-      <c r="P44">
-        <v>0.38073116448159372</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>0.36939854230779351</v>
-      </c>
-      <c r="C45">
-        <v>0.40704362912341241</v>
-      </c>
-      <c r="D45">
-        <v>0.40901686412499721</v>
-      </c>
-      <c r="E45">
-        <v>0.38663325304331869</v>
-      </c>
-      <c r="F45">
-        <v>0.35910056123489931</v>
-      </c>
-      <c r="G45">
-        <v>0.33303087742154908</v>
-      </c>
-      <c r="H45">
-        <v>0.32401800072109532</v>
-      </c>
-      <c r="I45">
-        <v>0.31991329903417531</v>
-      </c>
-      <c r="J45">
-        <v>0.30744551102974249</v>
-      </c>
-      <c r="K45">
-        <v>0.24075169843126329</v>
-      </c>
-      <c r="L45">
-        <v>0.2099964537665355</v>
-      </c>
-      <c r="M45">
-        <v>0.19665445285731301</v>
-      </c>
-      <c r="N45">
-        <v>0.15599475707437679</v>
-      </c>
-      <c r="O45">
-        <v>0.13016917541843881</v>
-      </c>
-      <c r="P45">
-        <v>0.14881265928940099</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>0.28325350589887471</v>
-      </c>
-      <c r="C46">
-        <v>0.38424353308790438</v>
-      </c>
-      <c r="D46">
-        <v>0.38652613590584017</v>
-      </c>
-      <c r="E46">
-        <v>0.35464208730051022</v>
-      </c>
-      <c r="F46">
-        <v>0.30306246639252682</v>
-      </c>
-      <c r="G46">
-        <v>0.31635899099246872</v>
-      </c>
-      <c r="H46">
-        <v>0.34290975491506709</v>
-      </c>
-      <c r="I46">
-        <v>0.3304580764957637</v>
-      </c>
-      <c r="J46">
-        <v>0.26264623288530559</v>
-      </c>
-      <c r="K46">
-        <v>0.23166843924627431</v>
-      </c>
-      <c r="L46">
-        <v>0.2141929895264581</v>
-      </c>
-      <c r="M46">
-        <v>0.17400576079609051</v>
-      </c>
-      <c r="N46">
-        <v>0.1482999234162152</v>
-      </c>
-      <c r="O46">
-        <v>0.1613212797226049</v>
-      </c>
-      <c r="P46">
-        <v>0.1730662618972649</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>0.38429981691475762</v>
-      </c>
-      <c r="C47">
-        <v>0.390532803043808</v>
-      </c>
-      <c r="D47">
-        <v>0.38347172915661198</v>
-      </c>
-      <c r="E47">
-        <v>0.38056878457831528</v>
-      </c>
-      <c r="F47">
-        <v>0.35426118283676261</v>
-      </c>
-      <c r="G47">
-        <v>0.35832017404432293</v>
-      </c>
-      <c r="H47">
-        <v>0.37584531915980163</v>
-      </c>
-      <c r="I47">
-        <v>0.37963513425090389</v>
-      </c>
-      <c r="J47">
-        <v>0.31431380720077767</v>
-      </c>
-      <c r="K47">
-        <v>0.31930197385208159</v>
-      </c>
-      <c r="L47">
-        <v>0.30788226164829979</v>
-      </c>
-      <c r="M47">
-        <v>0.29491384256783748</v>
-      </c>
-      <c r="N47">
-        <v>0.29924022583628862</v>
-      </c>
-      <c r="O47">
-        <v>0.29287479049026172</v>
-      </c>
-      <c r="P47">
-        <v>0.28259567198980129</v>
+        <v>0.2797112782504436</v>
+      </c>
+      <c r="Q43">
+        <v>0.2705050503948893</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>